--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1075,7 +1075,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1084,79 +1084,33 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>63.41</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>10.93%</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>27.29%</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>26.42%</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1876억</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8500</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>-15.00%</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>23500</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>176.47%</t>
-        </is>
-      </c>
+          <t>유진투자증권, 미래에셋증권</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
@@ -1164,7 +1118,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1173,53 +1127,53 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>714.52</v>
+        <v>63.41</v>
       </c>
       <c r="H9" t="n">
-        <v>666.78</v>
+        <v>2.85</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>27.29%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1228,22 +1182,22 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="P9" t="n">
-        <v>21500</v>
+        <v>8500</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-15.00%</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>14790</v>
+        <v>23500</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>176.47%</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1253,60 +1207,86 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H10" t="n">
-        <v>357</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O10" t="n">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="P10" t="n">
-        <v>4000</v>
+        <v>21500</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>2075</v>
+        <v>14790</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1316,86 +1296,60 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>50.4</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>5933억</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="P11" t="n">
-        <v>10960</v>
+        <v>4000</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>17990</v>
+        <v>2075</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>64.14%</t>
+          <t>-48.12%</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1405,45 +1359,61 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1248.47</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3.65%</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>76.55%</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1200억</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O12" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -1456,7 +1426,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1465,53 +1435,53 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>938.24</v>
+        <v>50.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1079.55</v>
+        <v>3.09</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>71.42%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30.00%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>17.59%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1129억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1520,44 +1490,32 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="P13" t="n">
-        <v>21000</v>
+        <v>10960</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>15380</v>
+        <v>17990</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>64.14%</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1566,7 +1524,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1576,7 +1534,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1586,7 +1544,7 @@
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>494.62</v>
+        <v>397.33</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
@@ -1608,92 +1566,244 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>케이앤에스아이앤씨</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>11000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>스펙</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>금융 지원 서비스업</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>494.62</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>해치텍</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>반도체 제조업</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>DB증권</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="G17" t="n">
         <v>101.91</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H17" t="n">
         <v>25.73</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>15.08%</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>5.63%</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>38.42%</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>37.69%</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>1269억</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>무</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="O17" t="n">
         <v>23000</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P17" t="n">
         <v>20500</v>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>-10.87%</t>
         </is>
       </c>
-      <c r="R15" t="n">
+      <c r="R17" t="n">
         <v>13930</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>-32.05%</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1102,10 +1102,18 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>26.76%</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -1398,7 +1406,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>76.55%</t>
+          <t>21.12%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W17"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1097,10 +1097,20 @@
           <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1109.37</v>
+      </c>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>98.72%</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
@@ -1108,13 +1118,19 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>10억</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>유</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="n">
+        <v>18000</v>
+      </c>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
@@ -1126,7 +1142,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1135,79 +1151,57 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>63.41</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.85</v>
-      </c>
+        <v>1109.37</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>10.93%</t>
-        </is>
-      </c>
+          <t>98.72%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>27.29%</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>26.42%</t>
-        </is>
-      </c>
+          <t>26.76%</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1876억</t>
+          <t>10억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P9" t="n">
-        <v>8500</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>-15.00%</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>23500</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>176.47%</t>
-        </is>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
@@ -1215,7 +1209,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1224,53 +1218,53 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>714.52</v>
+        <v>63.41</v>
       </c>
       <c r="H10" t="n">
-        <v>666.78</v>
+        <v>2.85</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>27.29%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1279,22 +1273,22 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="P10" t="n">
-        <v>21500</v>
+        <v>8500</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-15.00%</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>14790</v>
+        <v>23500</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>176.47%</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1304,60 +1298,86 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H11" t="n">
-        <v>357</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O11" t="n">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="P11" t="n">
-        <v>4000</v>
+        <v>21500</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>2075</v>
+        <v>14790</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1367,66 +1387,62 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1248.47</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3.65%</t>
-        </is>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>357</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>21.12%</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>1200억</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>2075</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>-48.12%</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1434,7 +1450,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1443,53 +1459,43 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.09</v>
-      </c>
+        <v>1248.47</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
+          <t>21.12%</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1200억</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1500,22 +1506,10 @@
       <c r="O13" t="n">
         <v>12000</v>
       </c>
-      <c r="P13" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R13" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
@@ -1523,50 +1517,88 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>50.4</v>
+      </c>
       <c r="H14" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+        <v>3.09</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>5933억</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O14" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P14" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -1574,245 +1606,296 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>30.00%</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>11000</v>
-      </c>
-      <c r="P15" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>90.91%</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>15380</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H16" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>101.91</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>38.42%</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1269억</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P17" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H18" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>38.42%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1269억</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O18" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,7 +537,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -546,79 +546,33 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>봉제의복 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>213.31</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>66.92%</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>66.92%</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1660억</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>유</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>28400</v>
-      </c>
-      <c r="P2" t="n">
-        <v>28000</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>-1.41%</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>18580</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>-33.64%</t>
-        </is>
-      </c>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -626,7 +580,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -635,59 +589,79 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>봉제의복 제조업</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>219.56</v>
+        <v>213.31</v>
       </c>
       <c r="H3" t="n">
-        <v>1047.78</v>
+        <v>5.63</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.98%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28.66%</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>66.92%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>66.92%</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1222억</t>
+          <t>1660억</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+        <v>28400</v>
+      </c>
+      <c r="P3" t="n">
+        <v>28000</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>-1.41%</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>18580</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-33.64%</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -695,7 +669,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -704,7 +678,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -714,43 +688,35 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>743.49</v>
+        <v>219.56</v>
       </c>
       <c r="H4" t="n">
-        <v>529.99</v>
+        <v>1047.78</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.26%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>39.42%</t>
-        </is>
-      </c>
+          <t>8.98%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>37.19%</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>32.49%</t>
-        </is>
-      </c>
+          <t>28.66%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2380억</t>
+          <t>1222억</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -759,24 +725,12 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>41200</v>
-      </c>
-      <c r="P4" t="n">
-        <v>40500</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>-1.70%</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>28650</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-29.26%</t>
-        </is>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -784,7 +738,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -793,77 +747,77 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>184.06</v>
+        <v>743.49</v>
       </c>
       <c r="H5" t="n">
-        <v>10.29</v>
+        <v>529.99</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.24%</t>
+          <t>39.42%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>36.93%</t>
+          <t>37.19%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>36.42%</t>
+          <t>32.49%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1532억</t>
+          <t>2380억</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>7000</v>
+        <v>41200</v>
       </c>
       <c r="P5" t="n">
-        <v>6000</v>
+        <v>40500</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-14.29%</t>
+          <t>-1.70%</t>
         </is>
       </c>
       <c r="R5" t="n">
-        <v>5140</v>
+        <v>28650</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-14.33%</t>
+          <t>-29.26%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -873,7 +827,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -882,99 +836,49 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>KB증권</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1146.41</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1706.71</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>17.93%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>77.50%</t>
-        </is>
-      </c>
+          <t>대신증권</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>41.03%</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>31.89%</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1579억</t>
-        </is>
-      </c>
+          <t>40.15%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>20700</v>
-      </c>
-      <c r="P6" t="n">
-        <v>30750</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>48.55%</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>22000</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-28.46%</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>31000.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>49.76%</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>51190.0</t>
-        </is>
-      </c>
+          <t>유</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -983,99 +887,87 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1238</v>
+        <v>184.06</v>
       </c>
       <c r="H7" t="n">
-        <v>1510.57</v>
+        <v>10.29</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>36.93%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>36.42%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1532억</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="P7" t="n">
-        <v>16560</v>
+        <v>6000</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>65.60%</t>
+          <t>-14.29%</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>9400</v>
+        <v>5140</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-43.24%</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>18740.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>87.40%</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>69621.0</t>
-        </is>
-      </c>
+          <t>-14.33%</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1084,65 +976,99 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>유진투자증권, 미래에셋증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1109.37</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>1146.41</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1706.71</v>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>98.72%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>17.93%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77.50%</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>26.76%</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>41.03%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>31.89%</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>18000</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+        <v>20700</v>
+      </c>
+      <c r="P8" t="n">
+        <v>30750</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>48.55%</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>22000</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-28.46%</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>31000.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>49.76%</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>51190.0</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1151,7 +1077,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1161,55 +1087,89 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>유진투자증권, 미래에셋증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1109.37</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>1238</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1510.57</v>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>98.72%</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>6.92%</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>74.17%</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>26.76%</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>33.19%</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>24.86%</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>18000</v>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="P9" t="n">
+        <v>16560</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>65.60%</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>9400</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>-43.24%</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>18740.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>87.40%</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>69621.0</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1218,79 +1178,57 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>63.41</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2.85</v>
-      </c>
+        <v>1109.37</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>10.93%</t>
-        </is>
-      </c>
+          <t>98.72%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>27.29%</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>26.42%</t>
-        </is>
-      </c>
+          <t>26.76%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1876억</t>
+          <t>10억</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P10" t="n">
-        <v>8500</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>-15.00%</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>23500</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>176.47%</t>
-        </is>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
@@ -1298,7 +1236,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1307,53 +1245,53 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>714.52</v>
+        <v>63.41</v>
       </c>
       <c r="H11" t="n">
-        <v>666.78</v>
+        <v>2.85</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>27.29%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1362,22 +1300,22 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="P11" t="n">
-        <v>21500</v>
+        <v>8500</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-15.00%</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>14790</v>
+        <v>23500</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>176.47%</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1387,60 +1325,86 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H12" t="n">
-        <v>357</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O12" t="n">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="P12" t="n">
-        <v>4000</v>
+        <v>21500</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>2075</v>
+        <v>14790</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1450,66 +1414,62 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>1248.47</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3.65%</t>
-        </is>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>357</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>21.12%</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>1200억</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>2075</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>-48.12%</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
@@ -1517,7 +1477,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1526,53 +1486,43 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.09</v>
-      </c>
+        <v>1248.47</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
+          <t>21.12%</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1200억</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1583,22 +1533,10 @@
       <c r="O14" t="n">
         <v>12000</v>
       </c>
-      <c r="P14" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -1606,50 +1544,88 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>50.4</v>
+      </c>
       <c r="H15" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+        <v>3.09</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5933억</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1657,245 +1633,296 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>30.00%</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>11000</v>
-      </c>
-      <c r="P16" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>90.91%</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>15380</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H17" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P17" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>101.91</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>38.42%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>1269억</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P18" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R18" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H19" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>38.42%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1269억</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,7 +559,11 @@
           <t>한국투자증권</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -580,7 +584,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -589,79 +593,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>봉제의복 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>213.31</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>66.92%</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>66.92%</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1660억</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>유</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>28400</v>
-      </c>
-      <c r="P3" t="n">
-        <v>28000</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>-1.41%</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>18580</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>-33.64%</t>
-        </is>
-      </c>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -669,7 +631,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -678,59 +640,79 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>봉제의복 제조업</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>219.56</v>
+        <v>213.31</v>
       </c>
       <c r="H4" t="n">
-        <v>1047.78</v>
+        <v>5.63</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.98%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>28.66%</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>66.92%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>66.92%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1222억</t>
+          <t>1660억</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+        <v>28400</v>
+      </c>
+      <c r="P4" t="n">
+        <v>28000</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>-1.41%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>18580</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>-33.64%</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -738,7 +720,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -747,7 +729,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -757,43 +739,35 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>743.49</v>
+        <v>219.56</v>
       </c>
       <c r="H5" t="n">
-        <v>529.99</v>
+        <v>1047.78</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.26%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>39.42%</t>
-        </is>
-      </c>
+          <t>8.98%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>37.19%</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>32.49%</t>
-        </is>
-      </c>
+          <t>28.66%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2380억</t>
+          <t>1222억</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -802,24 +776,12 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>41200</v>
-      </c>
-      <c r="P5" t="n">
-        <v>40500</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>-1.70%</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>28650</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>-29.26%</t>
-        </is>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
@@ -827,7 +789,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -836,41 +798,79 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대신증권</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>삼성증권</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>743.49</v>
+      </c>
+      <c r="H6" t="n">
+        <v>529.99</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>39.42%</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>40.15%</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>37.19%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>32.49%</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2380억</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>유</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>41200</v>
+      </c>
+      <c r="P6" t="n">
+        <v>40500</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>-1.70%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>28650</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-29.26%</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -878,7 +878,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -887,79 +887,57 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>184.06</v>
-      </c>
-      <c r="H7" t="n">
-        <v>10.29</v>
-      </c>
+        <v>868.64</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.10%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>6.24%</t>
-        </is>
-      </c>
+          <t>4.05%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>36.93%</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>36.42%</t>
-        </is>
-      </c>
+          <t>40.15%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1532억</t>
+          <t>2000억</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>7000</v>
-      </c>
-      <c r="P7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>-14.29%</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>5140</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-14.33%</t>
-        </is>
-      </c>
+        <v>14600</v>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -967,7 +945,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -976,53 +954,43 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1146.41</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1706.71</v>
-      </c>
+        <v>868.64</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17.93%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>77.50%</t>
-        </is>
-      </c>
+          <t>4.05%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>41.03%</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>31.89%</t>
-        </is>
-      </c>
+          <t>40.15%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1579억</t>
+          <t>2000억</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1031,44 +999,20 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>20700</v>
-      </c>
-      <c r="P8" t="n">
-        <v>30750</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>48.55%</t>
-        </is>
-      </c>
-      <c r="R8" t="n">
-        <v>22000</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>-28.46%</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>31000.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>49.76%</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>51190.0</t>
-        </is>
-      </c>
+        <v>14600</v>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1077,99 +1021,87 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1238</v>
+        <v>184.06</v>
       </c>
       <c r="H9" t="n">
-        <v>1510.57</v>
+        <v>10.29</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>36.93%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>36.42%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1532억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="P9" t="n">
-        <v>16560</v>
+        <v>6000</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>65.60%</t>
+          <t>-14.29%</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>9400</v>
+        <v>5140</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-43.24%</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>18740.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>87.40%</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>69621.0</t>
-        </is>
-      </c>
+          <t>-14.33%</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1178,65 +1110,99 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>유진투자증권, 미래에셋증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1109.37</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>1146.41</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1706.71</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>98.72%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>17.93%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.50%</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26.76%</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>41.03%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>31.89%</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>10억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>18000</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+        <v>20700</v>
+      </c>
+      <c r="P10" t="n">
+        <v>30750</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>48.55%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>22000</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-28.46%</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>31000.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>49.76%</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>51190.0</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1245,53 +1211,53 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>63.41</v>
+        <v>1238</v>
       </c>
       <c r="H11" t="n">
-        <v>2.85</v>
+        <v>1510.57</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>74.17%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>27.29%</t>
+          <t>33.19%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>24.86%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1876억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1303,29 +1269,41 @@
         <v>10000</v>
       </c>
       <c r="P11" t="n">
-        <v>8500</v>
+        <v>16560</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-15.00%</t>
+          <t>65.60%</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>23500</v>
+        <v>9400</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>176.47%</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+          <t>-43.24%</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>18740.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>87.40%</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>69621.0</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1334,79 +1312,57 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>714.52</v>
-      </c>
-      <c r="H12" t="n">
-        <v>666.78</v>
-      </c>
+        <v>1109.37</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>34.58%</t>
-        </is>
-      </c>
+          <t>98.72%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>33.00%</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>24.41%</t>
-        </is>
-      </c>
+          <t>26.76%</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>10억</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>21500</v>
-      </c>
-      <c r="P12" t="n">
-        <v>21500</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>14790</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>-31.21%</t>
-        </is>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1414,60 +1370,86 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>63.41</v>
+      </c>
       <c r="H13" t="n">
-        <v>357</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+        <v>2.85</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10.93%</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>27.29%</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>26.42%</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1876억</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O13" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="P13" t="n">
-        <v>4000</v>
+        <v>8500</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>-15.00%</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>2075</v>
+        <v>23500</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>176.47%</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1477,7 +1459,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1486,43 +1468,53 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1248.47</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>714.52</v>
+      </c>
+      <c r="H14" t="n">
+        <v>666.78</v>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.65%</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>21.12%</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1200억</t>
+          <t>1673억</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1531,12 +1523,24 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+        <v>21500</v>
+      </c>
+      <c r="P14" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>14790</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>-31.21%</t>
+        </is>
+      </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
@@ -1544,86 +1548,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>50.4</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>5933억</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="P15" t="n">
-        <v>10960</v>
+        <v>4000</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>17990</v>
+        <v>2075</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>64.14%</t>
+          <t>-48.12%</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1633,45 +1611,63 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1248.47</v>
+      </c>
       <c r="H16" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>1477.65</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3.65%</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>21.12%</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1200억</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O16" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -1684,7 +1680,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1693,53 +1689,53 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>938.24</v>
+        <v>50.4</v>
       </c>
       <c r="H17" t="n">
-        <v>1079.55</v>
+        <v>3.09</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>71.42%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30.00%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>17.59%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1129억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1748,44 +1744,32 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="P17" t="n">
-        <v>21000</v>
+        <v>10960</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>15380</v>
+        <v>17990</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>64.14%</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1794,7 +1778,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1804,7 +1788,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1814,7 +1798,7 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>494.62</v>
+        <v>397.33</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1836,92 +1820,244 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>케이앤에스아이앤씨</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>30.00%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>11000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>스펙</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>금융 지원 서비스업</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>494.62</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
         <v>14</v>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>해치텍</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>반도체 제조업</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>DB증권</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="G21" t="n">
         <v>101.91</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H21" t="n">
         <v>25.73</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>15.08%</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>5.63%</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>38.42%</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>37.69%</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>1269억</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>무</t>
         </is>
       </c>
-      <c r="O19" t="n">
+      <c r="O21" t="n">
         <v>23000</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P21" t="n">
         <v>20500</v>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>-10.87%</t>
         </is>
       </c>
-      <c r="R19" t="n">
+      <c r="R21" t="n">
         <v>13930</v>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>-32.05%</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,7 +584,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -593,37 +593,79 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>봉제의복 제조업</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>213.31</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>32.41%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>66.92%</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1664억</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>28400</v>
+      </c>
+      <c r="P3" t="n">
+        <v>28000</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>-1.41%</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>18580</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>-33.64%</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
@@ -631,7 +673,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -640,79 +682,59 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>봉제의복 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>213.31</v>
+        <v>219.56</v>
       </c>
       <c r="H4" t="n">
-        <v>5.63</v>
+        <v>1047.78</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
+          <t>8.98%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>66.92%</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>66.92%</t>
-        </is>
-      </c>
+          <t>28.61%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1660억</t>
+          <t>1222억</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>28400</v>
-      </c>
-      <c r="P4" t="n">
-        <v>28000</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>-1.41%</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>18580</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>-33.64%</t>
-        </is>
-      </c>
+        <v>10000</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -720,7 +742,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -729,7 +751,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -739,35 +761,43 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>219.56</v>
+        <v>743.49</v>
       </c>
       <c r="H5" t="n">
-        <v>1047.78</v>
+        <v>529.99</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.98%</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>39.42%</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>28.66%</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>37.15%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>32.49%</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>1222억</t>
+          <t>2380억</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -776,12 +806,24 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+        <v>41200</v>
+      </c>
+      <c r="P5" t="n">
+        <v>40500</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>-1.70%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>28650</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>-29.26%</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
@@ -789,7 +831,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -798,53 +840,43 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>743.49</v>
-      </c>
-      <c r="H6" t="n">
-        <v>529.99</v>
-      </c>
+        <v>868.64</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.26%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>39.42%</t>
-        </is>
-      </c>
+          <t>4.05%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>37.19%</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>32.49%</t>
-        </is>
-      </c>
+          <t>40.11%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2380억</t>
+          <t>2759억</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -853,24 +885,12 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>41200</v>
-      </c>
-      <c r="P6" t="n">
-        <v>40500</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>-1.70%</t>
-        </is>
-      </c>
-      <c r="R6" t="n">
-        <v>28650</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>-29.26%</t>
-        </is>
-      </c>
+        <v>14600</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -878,7 +898,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -887,57 +907,79 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>868.64</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>184.06</v>
+      </c>
+      <c r="H7" t="n">
+        <v>10.29</v>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.05%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>0.10%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6.24%</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>40.15%</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>36.89%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>36.42%</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2000억</t>
+          <t>1532억</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>14600</v>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+        <v>7000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>-14.29%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>5140</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-14.33%</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -945,7 +987,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -954,43 +996,53 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>868.64</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>1146.41</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1706.71</v>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.05%</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>17.93%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>77.50%</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>40.15%</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>41.03%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>31.89%</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2000억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -999,20 +1051,44 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>14600</v>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
+        <v>20700</v>
+      </c>
+      <c r="P8" t="n">
+        <v>30750</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>48.55%</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>22000</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>-28.46%</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>31000.0</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>49.76%</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>51190.0</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1021,87 +1097,99 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>184.06</v>
+        <v>1238</v>
       </c>
       <c r="H9" t="n">
-        <v>10.29</v>
+        <v>1510.57</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.24%</t>
+          <t>74.17%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>36.93%</t>
+          <t>33.19%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>36.42%</t>
+          <t>24.86%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1532억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="P9" t="n">
-        <v>6000</v>
+        <v>16560</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-14.29%</t>
+          <t>65.60%</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>5140</v>
+        <v>9400</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-14.33%</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+          <t>-43.24%</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>18740.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>87.40%</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>69621.0</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1110,99 +1198,55 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KB증권</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1146.41</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1706.71</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17.93%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>77.50%</t>
-        </is>
-      </c>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>41.03%</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>31.89%</t>
-        </is>
-      </c>
+          <t>26.42%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1579억</t>
+          <t>1875억</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>20700</v>
-      </c>
-      <c r="P10" t="n">
-        <v>30750</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>48.55%</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>22000</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-28.46%</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>31000.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>49.76%</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>51190.0</t>
-        </is>
-      </c>
+        <v>16500</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1211,7 +1255,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1221,89 +1265,55 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1238</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1510.57</v>
-      </c>
+        <v>1109.37</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.92%</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>74.17%</t>
-        </is>
-      </c>
+          <t>98.72%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>33.19%</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>24.86%</t>
-        </is>
-      </c>
+          <t>26.76%</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1849억</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P11" t="n">
-        <v>16560</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>65.60%</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>9400</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-43.24%</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>18740.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>87.40%</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>69621.0</t>
-        </is>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1312,57 +1322,79 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>유진투자증권, 미래에셋증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1109.37</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>63.41</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.85</v>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>98.72%</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10.93%</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26.76%</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>27.26%</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>26.42%</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>10억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8500</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>-15.00%</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>23500</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>176.47%</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1370,7 +1402,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1379,53 +1411,53 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>63.41</v>
+        <v>714.52</v>
       </c>
       <c r="H13" t="n">
-        <v>2.85</v>
+        <v>666.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>34.58%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>27.29%</t>
+          <t>33.00%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>24.41%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1876억</t>
+          <t>1673억</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1434,22 +1466,22 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>10000</v>
+        <v>21500</v>
       </c>
       <c r="P13" t="n">
-        <v>8500</v>
+        <v>21500</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-15.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>23500</v>
+        <v>14790</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>176.47%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1459,86 +1491,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>714.52</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>666.78</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>34.58%</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>33.00%</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>24.41%</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1673억</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>21500</v>
+        <v>2000</v>
       </c>
       <c r="P14" t="n">
-        <v>21500</v>
+        <v>4000</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>14790</v>
+        <v>2075</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>-48.12%</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1548,62 +1554,68 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1248.47</v>
+      </c>
       <c r="H15" t="n">
-        <v>357</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+        <v>1477.65</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3.65%</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>21.08%</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1202억</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P15" t="n">
-        <v>4000</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>2075</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-48.12%</t>
-        </is>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1611,7 +1623,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1620,45 +1632,53 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1248.47</v>
+        <v>50.4</v>
       </c>
       <c r="H16" t="n">
-        <v>1477.65</v>
+        <v>3.09</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.65%</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21.12%</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1200억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1669,10 +1689,22 @@
       <c r="O16" t="n">
         <v>12000</v>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1680,88 +1712,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>50.4</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>5933억</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1769,296 +1763,245 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H18" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>30.00%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>11000</v>
-      </c>
-      <c r="P19" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>90.91%</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
-        <v>15380</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>101.91</v>
+      </c>
       <c r="H20" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>25.73</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+        <v>23000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>해치텍</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>반도체 제조업</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>DB증권</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="H21" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>38.42%</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1269억</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P21" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R21" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,10 +1211,20 @@
           <t>IBK투자증권</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1187.74</v>
+      </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>21.75%</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
@@ -1229,7 +1239,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1246,7 +1256,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1255,52 +1265,52 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>유진투자증권, 미래에셋증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1109.37</v>
+        <v>1187.74</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>98.72%</t>
+          <t>21.75%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26.76%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1849억</t>
+          <t>1875억</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>18000</v>
+        <v>16500</v>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1313,7 +1323,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1322,79 +1332,59 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>63.41</v>
+        <v>1109.37</v>
       </c>
       <c r="H12" t="n">
-        <v>2.85</v>
+        <v>1375.08</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.17%</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>10.93%</t>
-        </is>
-      </c>
+          <t>98.72%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>27.26%</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>26.42%</t>
-        </is>
-      </c>
+          <t>26.76%</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1876억</t>
+          <t>1849억</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P12" t="n">
-        <v>8500</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>-15.00%</t>
-        </is>
-      </c>
-      <c r="R12" t="n">
-        <v>23500</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>176.47%</t>
-        </is>
-      </c>
+        <v>18000</v>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1402,7 +1392,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1411,53 +1401,53 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>714.52</v>
+        <v>63.41</v>
       </c>
       <c r="H13" t="n">
-        <v>666.78</v>
+        <v>2.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>27.26%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1466,22 +1456,22 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="P13" t="n">
-        <v>21500</v>
+        <v>8500</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-15.00%</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>14790</v>
+        <v>23500</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>176.47%</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1491,60 +1481,86 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H14" t="n">
-        <v>357</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O14" t="n">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="P14" t="n">
-        <v>4000</v>
+        <v>21500</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2075</v>
+        <v>14790</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1554,68 +1570,62 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1248.47</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>1477.65</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3.65%</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>21.08%</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1202억</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>2075</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>-48.12%</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1623,7 +1633,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1632,53 +1642,45 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>50.4</v>
+        <v>1248.47</v>
       </c>
       <c r="H16" t="n">
-        <v>3.09</v>
+        <v>1477.65</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
+          <t>21.08%</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1689,22 +1691,10 @@
       <c r="O16" t="n">
         <v>12000</v>
       </c>
-      <c r="P16" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1712,50 +1702,88 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>50.4</v>
+      </c>
       <c r="H17" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>3.09</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5933억</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P17" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1763,245 +1791,296 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>11000</v>
-      </c>
-      <c r="P18" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>90.91%</t>
-        </is>
-      </c>
-      <c r="R18" t="n">
-        <v>15380</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H19" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>101.91</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P20" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R20" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H21" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,7 +1256,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1265,52 +1265,54 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1187.74</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>1109.37</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1375.08</v>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>21.75%</t>
+          <t>98.72%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>26.76%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1875억</t>
+          <t>1849억</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>16500</v>
+        <v>18000</v>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1323,7 +1325,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1332,59 +1334,79 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>유진투자증권, 미래에셋증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1109.37</v>
+        <v>63.41</v>
       </c>
       <c r="H12" t="n">
-        <v>1375.08</v>
+        <v>2.85</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>98.72%</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>0.17%</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10.93%</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26.76%</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>27.26%</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>26.42%</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1849억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8500</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>-15.00%</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>23500</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>176.47%</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
@@ -1392,7 +1414,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1401,53 +1423,53 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>63.41</v>
+        <v>714.52</v>
       </c>
       <c r="H13" t="n">
-        <v>2.85</v>
+        <v>666.78</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>34.58%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>27.26%</t>
+          <t>33.00%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>24.41%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1876억</t>
+          <t>1673억</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1456,22 +1478,22 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>10000</v>
+        <v>21500</v>
       </c>
       <c r="P13" t="n">
-        <v>8500</v>
+        <v>21500</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-15.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>23500</v>
+        <v>14790</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>176.47%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1481,86 +1503,60 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>714.52</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>666.78</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>34.58%</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>33.00%</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>24.41%</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1673억</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>21500</v>
+        <v>2000</v>
       </c>
       <c r="P14" t="n">
-        <v>21500</v>
+        <v>4000</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>14790</v>
+        <v>2075</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>-48.12%</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1570,62 +1566,68 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1248.47</v>
+      </c>
       <c r="H15" t="n">
-        <v>357</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+        <v>1477.65</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3.65%</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>21.08%</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1202억</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P15" t="n">
-        <v>4000</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>2075</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-48.12%</t>
-        </is>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1633,7 +1635,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1642,45 +1644,53 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1248.47</v>
+        <v>50.4</v>
       </c>
       <c r="H16" t="n">
-        <v>1477.65</v>
+        <v>3.09</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.65%</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>21.08%</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1202억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1691,10 +1701,22 @@
       <c r="O16" t="n">
         <v>12000</v>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+      <c r="P16" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1702,88 +1724,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>50.4</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>5933억</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P17" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1791,296 +1775,245 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H18" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>11000</v>
-      </c>
-      <c r="P19" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>90.91%</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
-        <v>15380</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>101.91</v>
+      </c>
       <c r="H20" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>25.73</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+        <v>23000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>14</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>해치텍</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>반도체 제조업</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>DB증권</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="H21" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P21" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R21" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -564,15 +564,35 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>123.19</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.27%</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>22.19%</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1965억</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>10000</v>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -567,7 +567,9 @@
       <c r="G2" t="n">
         <v>123.19</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>57.15</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>0.27%</t>
@@ -881,7 +883,9 @@
       <c r="G6" t="n">
         <v>868.64</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>332.82</v>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>4.05%</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1243,7 +1243,9 @@
       <c r="G10" t="n">
         <v>1187.74</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>1676.26</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>21.75%</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -753,10 +753,22 @@
       <c r="O4" t="n">
         <v>10000</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>25250</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>152.50%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>36900</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>46.14%</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
@@ -1313,20 +1325,28 @@
         <v>1109.37</v>
       </c>
       <c r="H11" t="n">
-        <v>1375.08</v>
+        <v>1307.78</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>98.72%</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>78.39%</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>26.76%</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>18.35%</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>1849억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1325,7 +1325,7 @@
         <v>1109.37</v>
       </c>
       <c r="H11" t="n">
-        <v>1307.78</v>
+        <v>1375.08</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1810,10 +1810,22 @@
       <c r="O17" t="n">
         <v>2000</v>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>1905</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-52.37%</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1962,10 +1974,22 @@
       <c r="O19" t="n">
         <v>2000</v>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>3415</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>70.75%</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>1937</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-43.28%</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1670,10 +1670,22 @@
       <c r="O15" t="n">
         <v>12000</v>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>42750</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>256.25%</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>45700</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>6.90%</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -575,13 +575,21 @@
           <t>0.27%</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>22.19%</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>17.15%</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>1965억</t>
@@ -733,13 +741,21 @@
           <t>8.98%</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>44.02%</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>28.61%</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>23.21%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>1222억</t>
@@ -903,13 +919,21 @@
           <t>4.05%</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>57.26%</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>40.11%</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>33.29%</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>2759억</t>
@@ -1263,13 +1287,21 @@
           <t>21.75%</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>85.39%</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>26.42%</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>21.01%</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>1875억</t>
@@ -1650,13 +1682,21 @@
           <t>3.65%</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>55.61%</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>21.08%</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>14.42%</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>1202억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1396,9 +1396,21 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>52300.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>190.56%</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>307743.0</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,10 +603,22 @@
       <c r="O2" t="n">
         <v>10000</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>21150</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>111.50%</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>14500</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>-31.44%</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
@@ -1249,7 +1261,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1258,7 +1270,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1268,43 +1280,33 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1187.74</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1676.26</v>
-      </c>
+        <v>1136.84</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21.75%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>85.39%</t>
-        </is>
-      </c>
+          <t>36.07%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>26.42%</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>21.01%</t>
-        </is>
-      </c>
+          <t>34.50%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1875억</t>
+          <t>1550억</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1313,7 +1315,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>16500</v>
+        <v>12300</v>
       </c>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1326,7 +1328,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1335,87 +1337,75 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>유진투자증권, 미래에셋증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1109.37</v>
+        <v>1187.74</v>
       </c>
       <c r="H11" t="n">
-        <v>1375.08</v>
+        <v>1676.26</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>98.72%</t>
+          <t>21.75%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.39%</t>
+          <t>85.39%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26.76%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>18.35%</t>
+          <t>21.01%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1849억</t>
+          <t>1875억</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>18000</v>
+        <v>16500</v>
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>52300.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>190.56%</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>307743.0</t>
-        </is>
-      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1424,87 +1414,99 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>63.41</v>
+        <v>1109.37</v>
       </c>
       <c r="H12" t="n">
-        <v>2.85</v>
+        <v>1375.08</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>98.72%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>78.39%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>27.26%</t>
+          <t>26.76%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>18.35%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1876억</t>
+          <t>1849억</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="P12" t="n">
-        <v>8500</v>
+        <v>56000</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-15.00%</t>
+          <t>211.11%</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>23500</v>
+        <v>27050</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>176.47%</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+          <t>-51.70%</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>52300.0</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>190.56%</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>307743.0</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1513,53 +1515,53 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>714.52</v>
+        <v>63.41</v>
       </c>
       <c r="H13" t="n">
-        <v>666.78</v>
+        <v>2.85</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>27.26%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1568,22 +1570,22 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="P13" t="n">
-        <v>21500</v>
+        <v>8500</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-15.00%</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>14790</v>
+        <v>23500</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>176.47%</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1593,60 +1595,86 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H14" t="n">
-        <v>357</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O14" t="n">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="P14" t="n">
-        <v>4000</v>
+        <v>21500</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>2075</v>
+        <v>14790</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1656,86 +1684,60 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1248.47</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>1477.65</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3.65%</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>55.61%</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>21.08%</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>14.42%</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1202억</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="P15" t="n">
-        <v>42750</v>
+        <v>4000</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>256.25%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>45700</v>
+        <v>2075</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>6.90%</t>
+          <t>-48.12%</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1745,7 +1747,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1754,53 +1756,53 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>50.4</v>
+        <v>1248.47</v>
       </c>
       <c r="H16" t="n">
-        <v>3.09</v>
+        <v>1477.65</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>55.61%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>25.60%</t>
+          <t>21.08%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>25.36%</t>
+          <t>14.42%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1812,19 +1814,19 @@
         <v>12000</v>
       </c>
       <c r="P16" t="n">
-        <v>10960</v>
+        <v>42750</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>256.25%</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>17990</v>
+        <v>45700</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>64.14%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -1834,60 +1836,86 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>50.4</v>
+      </c>
       <c r="H17" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>3.09</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5933억</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="P17" t="n">
-        <v>4000</v>
+        <v>10960</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>1905</v>
+        <v>17990</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>-52.37%</t>
+          <t>64.14%</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -1897,250 +1925,224 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P18" t="n">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>15380</v>
+        <v>1905</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-52.37%</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H19" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="P19" t="n">
-        <v>3415</v>
+        <v>21000</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>70.75%</t>
+          <t>90.91%</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>1937</v>
+        <v>15380</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>101.91</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="P20" t="n">
-        <v>20500</v>
+        <v>3415</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-10.87%</t>
+          <t>70.75%</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>13930</v>
+        <v>1937</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-32.05%</t>
+          <t>-43.28%</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2148,6 +2150,95 @@
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H21" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O21" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -959,10 +959,22 @@
       <c r="O6" t="n">
         <v>14600</v>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>27100</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>85.62%</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>16830</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>-37.90%</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
@@ -1398,9 +1410,21 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>61100.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>270.30%</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>332800.0</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1925,62 +1949,66 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1097.62</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>58.44%</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>890억</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4000</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="R18" t="n">
-        <v>1905</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>-52.37%</t>
-        </is>
-      </c>
+        <v>23500</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -1988,250 +2016,224 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P19" t="n">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>15380</v>
+        <v>1905</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-52.37%</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H20" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="P20" t="n">
-        <v>3415</v>
+        <v>21000</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>70.75%</t>
+          <t>90.91%</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>1937</v>
+        <v>15380</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>101.91</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="P21" t="n">
-        <v>20500</v>
+        <v>3415</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-10.87%</t>
+          <t>70.75%</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>13930</v>
+        <v>1937</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>-32.05%</t>
+          <t>-43.28%</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2239,6 +2241,95 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H22" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1406,10 +1406,22 @@
       <c r="O11" t="n">
         <v>16500</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>61800</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>274.55%</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>31100</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-49.68%</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>61100.0</t>
@@ -1999,7 +2011,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O18" t="n">

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1303,7 +1303,9 @@
       <c r="G10" t="n">
         <v>1136.84</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>1741.48</v>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>36.07%</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1785,7 +1785,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1794,79 +1794,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1248.47</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1477.65</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>3.65%</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>55.61%</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>21.08%</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>14.42%</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1202억</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P16" t="n">
-        <v>42750</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>256.25%</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>45700</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>6.90%</t>
-        </is>
-      </c>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1874,7 +1832,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1883,53 +1841,53 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>50.4</v>
+        <v>1248.47</v>
       </c>
       <c r="H17" t="n">
-        <v>3.09</v>
+        <v>1477.65</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>55.61%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>25.60%</t>
+          <t>21.08%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>25.36%</t>
+          <t>14.42%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1941,19 +1899,19 @@
         <v>12000</v>
       </c>
       <c r="P17" t="n">
-        <v>10960</v>
+        <v>42750</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>256.25%</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>17990</v>
+        <v>45700</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>64.14%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -1963,7 +1921,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1972,57 +1930,79 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1097.62</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>50.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.09</v>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5.29%</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>58.44%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>890억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O18" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -2030,62 +2010,66 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1097.62</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>58.44%</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>890억</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
-        <v>1905</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>-52.37%</t>
-        </is>
-      </c>
+        <v>23500</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
@@ -2093,250 +2077,224 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P20" t="n">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>15380</v>
+        <v>1905</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-52.37%</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H21" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="P21" t="n">
-        <v>3415</v>
+        <v>21000</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>70.75%</t>
+          <t>90.91%</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>1937</v>
+        <v>15380</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>101.91</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="P22" t="n">
-        <v>20500</v>
+        <v>3415</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-10.87%</t>
+          <t>70.75%</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>13930</v>
+        <v>1937</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-32.05%</t>
+          <t>-43.28%</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2344,6 +2302,95 @@
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H23" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1809,18 +1809,38 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>388.84</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>13.70%</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>20.77%</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>10072억</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O16" t="n">
+        <v>90500</v>
+      </c>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
@@ -1832,7 +1852,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1841,53 +1861,43 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1248.47</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1477.65</v>
-      </c>
+        <v>388.84</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.65%</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>55.61%</t>
-        </is>
-      </c>
+          <t>13.70%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21.08%</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>14.42%</t>
-        </is>
-      </c>
+          <t>20.77%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1202억</t>
+          <t>10072억</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1896,24 +1906,12 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P17" t="n">
-        <v>42750</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>256.25%</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>45700</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>6.90%</t>
-        </is>
-      </c>
+        <v>90500</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1921,7 +1919,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1930,53 +1928,53 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>50.4</v>
+        <v>1248.47</v>
       </c>
       <c r="H18" t="n">
-        <v>3.09</v>
+        <v>1477.65</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>55.61%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>25.60%</t>
+          <t>21.08%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>25.36%</t>
+          <t>14.42%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1988,19 +1986,19 @@
         <v>12000</v>
       </c>
       <c r="P18" t="n">
-        <v>10960</v>
+        <v>42750</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>256.25%</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>17990</v>
+        <v>45700</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>64.14%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2010,7 +2008,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2019,57 +2017,79 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1097.62</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>50.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.09</v>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5.29%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>58.44%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>890억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
@@ -2077,62 +2097,68 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1097.62</v>
+      </c>
       <c r="H20" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>685.33</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>58.44%</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>890억</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P20" t="n">
-        <v>4000</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="R20" t="n">
-        <v>1905</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>-52.37%</t>
-        </is>
-      </c>
+        <v>23500</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -2140,250 +2166,224 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P21" t="n">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>15380</v>
+        <v>1905</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-52.37%</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H22" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O22" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="P22" t="n">
-        <v>3415</v>
+        <v>21000</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>70.75%</t>
+          <t>90.91%</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>1937</v>
+        <v>15380</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>101.91</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="P23" t="n">
-        <v>20500</v>
+        <v>3415</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-10.87%</t>
+          <t>70.75%</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>13930</v>
+        <v>1937</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>-32.05%</t>
+          <t>-43.28%</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2391,6 +2391,95 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H24" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P24" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1852,7 +1852,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1861,43 +1861,53 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>388.84</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>1248.47</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1477.65</v>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13.70%</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>55.61%</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>20.77%</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>21.08%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>14.42%</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>10072억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1906,12 +1916,24 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>90500</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P17" t="n">
+        <v>42750</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>256.25%</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>45700</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>6.90%</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1919,7 +1941,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1928,53 +1950,53 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1248.47</v>
+        <v>50.4</v>
       </c>
       <c r="H18" t="n">
-        <v>1477.65</v>
+        <v>3.09</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>55.61%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>21.08%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>14.42%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1202억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1986,19 +2008,19 @@
         <v>12000</v>
       </c>
       <c r="P18" t="n">
-        <v>42750</v>
+        <v>10960</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>256.25%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>45700</v>
+        <v>17990</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>6.90%</t>
+          <t>64.14%</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2008,7 +2030,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2017,79 +2039,59 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>50.4</v>
+        <v>1097.62</v>
       </c>
       <c r="H19" t="n">
-        <v>3.09</v>
+        <v>685.33</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
+          <t>58.44%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>890억</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P19" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+        <v>23500</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
@@ -2097,68 +2099,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1097.62</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>685.33</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5.29%</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>58.44%</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>890억</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>유</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>1905</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-52.37%</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -2166,224 +2162,250 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H21" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O21" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="P21" t="n">
-        <v>4000</v>
+        <v>21000</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>90.91%</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>1905</v>
+        <v>15380</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>-52.37%</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P22" t="n">
-        <v>21000</v>
+        <v>3415</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>70.75%</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>15380</v>
+        <v>1937</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-43.28%</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>101.91</v>
+      </c>
       <c r="H23" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+        <v>25.73</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O23" t="n">
-        <v>2000</v>
+        <v>23000</v>
       </c>
       <c r="P23" t="n">
-        <v>3415</v>
+        <v>20500</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>70.75%</t>
+          <t>-10.87%</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>1937</v>
+        <v>13930</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>-43.28%</t>
+          <t>-32.05%</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2391,95 +2413,6 @@
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>14</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>해치텍</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>반도체 제조업</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>DB증권</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="H24" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P24" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R24" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1311,13 +1311,21 @@
           <t>36.07%</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>73.94%</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>34.50%</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>23.79%</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>1550억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1823,7 +1823,9 @@
       <c r="G16" t="n">
         <v>388.84</v>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>408.16</v>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>13.70%</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -982,7 +982,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -991,79 +991,45 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>대신증권, 유진투자증권</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>184.06</v>
-      </c>
-      <c r="H7" t="n">
-        <v>10.29</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.10%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>6.24%</t>
-        </is>
-      </c>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>36.89%</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>36.42%</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1532억</t>
-        </is>
-      </c>
+          <t>15.15%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>유</t>
         </is>
       </c>
-      <c r="O7" t="n">
-        <v>7000</v>
-      </c>
-      <c r="P7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>-14.29%</t>
-        </is>
-      </c>
-      <c r="R7" t="n">
-        <v>5140</v>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>-14.33%</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -1071,7 +1037,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1080,99 +1046,87 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1146.41</v>
+        <v>184.06</v>
       </c>
       <c r="H8" t="n">
-        <v>1706.71</v>
+        <v>10.29</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>17.93%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.50%</t>
+          <t>6.24%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>41.03%</t>
+          <t>36.89%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>31.89%</t>
+          <t>36.42%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>1579억</t>
+          <t>1532억</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>20700</v>
+        <v>7000</v>
       </c>
       <c r="P8" t="n">
-        <v>30750</v>
+        <v>6000</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>48.55%</t>
+          <t>-14.29%</t>
         </is>
       </c>
       <c r="R8" t="n">
-        <v>22000</v>
+        <v>5140</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-28.46%</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>31000.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>49.76%</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>51190.0</t>
-        </is>
-      </c>
+          <t>-14.33%</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1181,12 +1135,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1196,38 +1150,38 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1238</v>
+        <v>1146.41</v>
       </c>
       <c r="H9" t="n">
-        <v>1510.57</v>
+        <v>1706.71</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>17.93%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>77.50%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>41.03%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>31.89%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1236,44 +1190,44 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>10000</v>
+        <v>20700</v>
       </c>
       <c r="P9" t="n">
-        <v>16560</v>
+        <v>30750</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>65.60%</t>
+          <t>48.55%</t>
         </is>
       </c>
       <c r="R9" t="n">
-        <v>9400</v>
+        <v>22000</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-43.24%</t>
+          <t>-28.46%</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>18740.0</t>
+          <t>31000.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>87.40%</t>
+          <t>49.76%</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>69621.0</t>
+          <t>51190.0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1282,53 +1236,53 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1136.84</v>
+        <v>1238</v>
       </c>
       <c r="H10" t="n">
-        <v>1741.48</v>
+        <v>1510.57</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>36.07%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>73.94%</t>
+          <t>74.17%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>34.50%</t>
+          <t>33.19%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>23.79%</t>
+          <t>24.86%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1550억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1337,20 +1291,44 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>12300</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>16560</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>65.60%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>9400</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-43.24%</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>18740.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>87.40%</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>69621.0</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1359,7 +1337,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1369,43 +1347,43 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1187.74</v>
+        <v>1136.84</v>
       </c>
       <c r="H11" t="n">
-        <v>1676.26</v>
+        <v>1741.48</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>21.75%</t>
+          <t>36.07%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>85.39%</t>
+          <t>73.94%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>34.50%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>21.01%</t>
+          <t>23.79%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1875억</t>
+          <t>1550억</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1414,44 +1392,20 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>16500</v>
-      </c>
-      <c r="P11" t="n">
-        <v>61800</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>274.55%</t>
-        </is>
-      </c>
-      <c r="R11" t="n">
-        <v>31100</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>-49.68%</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>61100.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>270.30%</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>332800.0</t>
-        </is>
-      </c>
+        <v>12300</v>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1460,99 +1414,99 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>유진투자증권, 미래에셋증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1109.37</v>
+        <v>1187.74</v>
       </c>
       <c r="H12" t="n">
-        <v>1375.08</v>
+        <v>1676.26</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>98.72%</t>
+          <t>21.75%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.39%</t>
+          <t>85.39%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26.76%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>18.35%</t>
+          <t>21.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1849억</t>
+          <t>1875억</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>18000</v>
+        <v>16500</v>
       </c>
       <c r="P12" t="n">
-        <v>56000</v>
+        <v>61800</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>211.11%</t>
+          <t>274.55%</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>27050</v>
+        <v>31100</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-51.70%</t>
+          <t>-49.68%</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>52300.0</t>
+          <t>61100.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>190.56%</t>
+          <t>270.30%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>307743.0</t>
+          <t>332800.0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1561,87 +1515,99 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>63.41</v>
+        <v>1109.37</v>
       </c>
       <c r="H13" t="n">
-        <v>2.85</v>
+        <v>1375.08</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>98.72%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>78.39%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>27.26%</t>
+          <t>26.76%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>18.35%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1876억</t>
+          <t>1849억</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="P13" t="n">
-        <v>8500</v>
+        <v>56000</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-15.00%</t>
+          <t>211.11%</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>23500</v>
+        <v>27050</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>176.47%</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+          <t>-51.70%</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>52300.0</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>190.56%</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>307743.0</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1650,53 +1616,53 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>714.52</v>
+        <v>63.41</v>
       </c>
       <c r="H14" t="n">
-        <v>666.78</v>
+        <v>2.85</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>27.26%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1705,22 +1671,22 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>21500</v>
+        <v>10000</v>
       </c>
       <c r="P14" t="n">
-        <v>21500</v>
+        <v>8500</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-15.00%</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>14790</v>
+        <v>23500</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>176.47%</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1730,60 +1696,86 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H15" t="n">
-        <v>357</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O15" t="n">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="P15" t="n">
-        <v>4000</v>
+        <v>21500</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>2075</v>
+        <v>14790</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1793,68 +1785,62 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>388.84</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>408.16</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>13.70%</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>20.77%</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>10072억</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>90500</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>2075</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-48.12%</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1862,7 +1848,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1871,53 +1857,45 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1248.47</v>
+        <v>388.84</v>
       </c>
       <c r="H17" t="n">
-        <v>1477.65</v>
+        <v>408.16</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.65%</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>55.61%</t>
-        </is>
-      </c>
+          <t>13.70%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>21.08%</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>14.42%</t>
-        </is>
-      </c>
+          <t>20.77%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1202억</t>
+          <t>10072억</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1926,24 +1904,12 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P17" t="n">
-        <v>42750</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>256.25%</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>45700</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>6.90%</t>
-        </is>
-      </c>
+        <v>90500</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1951,7 +1917,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1960,53 +1926,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3.09</v>
-      </c>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
+          <t>30.62%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
+          <t>23.33%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>2122억</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2015,24 +1969,12 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P18" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R18" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+        <v>7800</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -2040,7 +1982,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2049,59 +1991,79 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1097.62</v>
+        <v>1248.47</v>
       </c>
       <c r="H19" t="n">
-        <v>685.33</v>
+        <v>1477.65</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5.29%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>55.61%</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>58.44%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>21.08%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>14.42%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>890억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>42750</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>256.25%</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>45700</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>6.90%</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
@@ -2109,60 +2071,86 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>50.4</v>
+      </c>
       <c r="H20" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>3.09</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>5933억</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O20" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="P20" t="n">
-        <v>4000</v>
+        <v>10960</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>1905</v>
+        <v>17990</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-52.37%</t>
+          <t>64.14%</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2172,7 +2160,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2181,99 +2169,75 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>938.24</v>
+        <v>1097.62</v>
       </c>
       <c r="H21" t="n">
-        <v>1079.55</v>
+        <v>685.83</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>5.29%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>71.42%</t>
+          <t>72.75%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>30.03%</t>
+          <t>58.44%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>17.59%</t>
+          <t>46.16%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1129억</t>
+          <t>890억</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>11000</v>
-      </c>
-      <c r="P21" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>90.91%</t>
-        </is>
-      </c>
-      <c r="R21" t="n">
-        <v>15380</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+        <v>23500</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2282,7 +2246,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2292,7 +2256,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2302,7 +2266,7 @@
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>494.62</v>
+        <v>397.33</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -2314,19 +2278,19 @@
         <v>2000</v>
       </c>
       <c r="P22" t="n">
-        <v>3415</v>
+        <v>4000</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>70.75%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R22" t="n">
-        <v>1937</v>
+        <v>1905</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>-43.28%</t>
+          <t>-52.37%</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2336,92 +2300,256 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>케이앤에스아이앤씨</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>IBK투자증권</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>11000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>스펙</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>금융 지원 서비스업</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>494.62</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P24" t="n">
+        <v>3415</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>70.75%</t>
+        </is>
+      </c>
+      <c r="R24" t="n">
+        <v>1937</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>-43.28%</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
         <v>14</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>해치텍</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>반도체 제조업</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>DB증권</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="G25" t="n">
         <v>101.91</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H25" t="n">
         <v>25.73</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>15.08%</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>5.63%</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>38.35%</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>37.69%</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>1271억</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>무</t>
         </is>
       </c>
-      <c r="O23" t="n">
+      <c r="O25" t="n">
         <v>23000</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P25" t="n">
         <v>20500</v>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>-10.87%</t>
         </is>
       </c>
-      <c r="R23" t="n">
+      <c r="R25" t="n">
         <v>13930</v>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>-32.05%</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1009,23 +1009,35 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>983.98</v>
+      </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>13.31%</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>15.15%</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2753억</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>유</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>18500</v>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -2191,7 +2203,7 @@
         <v>1097.62</v>
       </c>
       <c r="H21" t="n">
-        <v>685.83</v>
+        <v>685.33</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1891,20 +1891,28 @@
         <v>388.84</v>
       </c>
       <c r="H17" t="n">
-        <v>408.16</v>
+        <v>408.17</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>13.70%</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>31.33%</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>20.77%</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>16.08%</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>10072억</t>
@@ -1957,7 +1965,9 @@
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>1538.51</v>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>30.62%</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1708,7 +1708,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1717,53 +1717,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>714.52</v>
-      </c>
-      <c r="H15" t="n">
-        <v>666.78</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>34.58%</t>
-        </is>
-      </c>
+          <t>SK증권</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>33.00%</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>24.41%</t>
-        </is>
-      </c>
+          <t>97.45%</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>133억</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1772,24 +1752,12 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>21500</v>
-      </c>
-      <c r="P15" t="n">
-        <v>21500</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>14790</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>-31.21%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1797,60 +1765,86 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H16" t="n">
-        <v>357</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O16" t="n">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="P16" t="n">
-        <v>4000</v>
+        <v>21500</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R16" t="n">
-        <v>2075</v>
+        <v>14790</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -1860,76 +1854,62 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>388.84</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>408.17</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>13.70%</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>31.33%</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>20.77%</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>16.08%</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>10072억</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>90500</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>2075</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-48.12%</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1937,7 +1917,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1946,43 +1926,53 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>388.84</v>
+      </c>
       <c r="H18" t="n">
-        <v>1538.51</v>
+        <v>408.16</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>30.62%</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>13.70%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>31.33%</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>23.33%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>20.77%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>16.08%</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2122억</t>
+          <t>10072억</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1991,7 +1981,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>7800</v>
+        <v>90500</v>
       </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -2004,7 +1994,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2013,53 +2003,43 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1248.47</v>
-      </c>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1477.65</v>
+        <v>1538.51</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.65%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>55.61%</t>
-        </is>
-      </c>
+          <t>30.62%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>21.08%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>14.42%</t>
-        </is>
-      </c>
+          <t>23.33%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1202억</t>
+          <t>2122억</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2068,24 +2048,12 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P19" t="n">
-        <v>42750</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>256.25%</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
-        <v>45700</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>6.90%</t>
-        </is>
-      </c>
+        <v>7800</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
@@ -2093,7 +2061,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2102,53 +2070,53 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>50.4</v>
+        <v>1248.47</v>
       </c>
       <c r="H20" t="n">
-        <v>3.09</v>
+        <v>1477.65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>55.61%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>25.60%</t>
+          <t>21.08%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25.36%</t>
+          <t>14.42%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2160,19 +2128,19 @@
         <v>12000</v>
       </c>
       <c r="P20" t="n">
-        <v>10960</v>
+        <v>42750</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>256.25%</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>17990</v>
+        <v>45700</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>64.14%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2182,7 +2150,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2191,67 +2159,79 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1097.62</v>
+        <v>50.4</v>
       </c>
       <c r="H21" t="n">
-        <v>685.33</v>
+        <v>3.09</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>72.75%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>58.44%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>46.16%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>890억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -2259,62 +2239,76 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1097.62</v>
+      </c>
       <c r="H22" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+        <v>685.33</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>72.75%</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>58.44%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>46.16%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>890억</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O22" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P22" t="n">
-        <v>4000</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="R22" t="n">
-        <v>1905</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>-52.37%</t>
-        </is>
-      </c>
+        <v>23500</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2322,250 +2316,224 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P23" t="n">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>15380</v>
+        <v>1905</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-52.37%</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H24" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O24" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="P24" t="n">
-        <v>3415</v>
+        <v>21000</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>70.75%</t>
+          <t>90.91%</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>1937</v>
+        <v>15380</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>101.91</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="P25" t="n">
-        <v>20500</v>
+        <v>3415</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-10.87%</t>
+          <t>70.75%</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>13930</v>
+        <v>1937</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-32.05%</t>
+          <t>-43.28%</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2573,6 +2541,95 @@
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H26" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P26" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,7 +1012,9 @@
       <c r="G7" t="n">
         <v>983.98</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>986.9400000000001</v>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>13.31%</t>
@@ -1730,7 +1732,11 @@
           <t>SK증권</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1765,7 +1771,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1774,53 +1780,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>714.52</v>
-      </c>
-      <c r="H16" t="n">
-        <v>666.78</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>34.58%</t>
-        </is>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>33.00%</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>24.41%</t>
-        </is>
-      </c>
+          <t>97.45%</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>133억</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1829,24 +1819,12 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>21500</v>
-      </c>
-      <c r="P16" t="n">
-        <v>21500</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>14790</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>-31.21%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1854,60 +1832,86 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H17" t="n">
-        <v>357</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="P17" t="n">
-        <v>4000</v>
+        <v>21500</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>2075</v>
+        <v>14790</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -1917,76 +1921,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>388.84</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>408.16</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13.70%</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>31.33%</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>20.77%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>16.08%</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>10072억</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>90500</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>2075</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-48.12%</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -1994,7 +1984,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2003,43 +1993,53 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>388.84</v>
+      </c>
       <c r="H19" t="n">
-        <v>1538.51</v>
+        <v>408.16</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30.62%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>13.70%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>31.33%</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>23.33%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>20.77%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>16.08%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2122억</t>
+          <t>10072억</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2048,7 +2048,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>7800</v>
+        <v>90500</v>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2070,53 +2070,43 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1248.47</v>
-      </c>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1477.65</v>
+        <v>1538.51</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.65%</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>55.61%</t>
-        </is>
-      </c>
+          <t>30.62%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21.08%</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>14.42%</t>
-        </is>
-      </c>
+          <t>23.33%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1202억</t>
+          <t>2122억</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2125,24 +2115,12 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P20" t="n">
-        <v>42750</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>256.25%</t>
-        </is>
-      </c>
-      <c r="R20" t="n">
-        <v>45700</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>6.90%</t>
-        </is>
-      </c>
+        <v>7800</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -2150,7 +2128,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2159,53 +2137,53 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>50.4</v>
+        <v>1248.47</v>
       </c>
       <c r="H21" t="n">
-        <v>3.09</v>
+        <v>1477.65</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>55.61%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>25.60%</t>
+          <t>21.08%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>25.36%</t>
+          <t>14.42%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2217,19 +2195,19 @@
         <v>12000</v>
       </c>
       <c r="P21" t="n">
-        <v>10960</v>
+        <v>42750</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>256.25%</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>17990</v>
+        <v>45700</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>64.14%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2239,7 +2217,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2248,67 +2226,79 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1097.62</v>
+        <v>50.4</v>
       </c>
       <c r="H22" t="n">
-        <v>685.33</v>
+        <v>3.09</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>72.75%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>58.44%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>46.16%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>890억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2316,62 +2306,76 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1097.62</v>
+      </c>
       <c r="H23" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+        <v>685.33</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>72.75%</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>58.44%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>46.16%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>890억</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O23" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P23" t="n">
-        <v>4000</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="R23" t="n">
-        <v>1905</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>-52.37%</t>
-        </is>
-      </c>
+        <v>23500</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
@@ -2379,250 +2383,224 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P24" t="n">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>15380</v>
+        <v>1905</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-52.37%</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H25" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O25" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="P25" t="n">
-        <v>3415</v>
+        <v>21000</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>70.75%</t>
+          <t>90.91%</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>1937</v>
+        <v>15380</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>101.91</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="n">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="P26" t="n">
-        <v>20500</v>
+        <v>3415</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-10.87%</t>
+          <t>70.75%</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>13930</v>
+        <v>1937</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>-32.05%</t>
+          <t>-43.28%</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -2630,6 +2608,95 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H27" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P27" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1412,9 +1412,21 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>27450.0</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>123.17%</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>180493.0</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1771,7 +1783,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1780,37 +1792,53 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>714.52</v>
+      </c>
+      <c r="H16" t="n">
+        <v>666.78</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>97.45%</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>133억</t>
+          <t>1673억</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1819,12 +1847,24 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+        <v>21500</v>
+      </c>
+      <c r="P16" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>14790</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>-31.21%</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1832,86 +1872,60 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>714.52</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>666.78</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>34.58%</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>33.00%</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>24.41%</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1673억</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>21500</v>
+        <v>2000</v>
       </c>
       <c r="P17" t="n">
-        <v>21500</v>
+        <v>4000</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>14790</v>
+        <v>2075</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>-48.12%</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -1921,62 +1935,76 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>388.84</v>
+      </c>
       <c r="H18" t="n">
-        <v>357</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>408.16</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>13.70%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>31.33%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>20.77%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>16.08%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>10072억</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P18" t="n">
-        <v>4000</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="R18" t="n">
-        <v>2075</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>-48.12%</t>
-        </is>
-      </c>
+        <v>90500</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -1984,7 +2012,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1993,53 +2021,43 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>388.84</v>
-      </c>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>408.16</v>
+        <v>1538.51</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13.70%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>31.33%</t>
-        </is>
-      </c>
+          <t>30.62%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20.77%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>16.08%</t>
-        </is>
-      </c>
+          <t>23.33%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>10072억</t>
+          <t>2122억</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2048,7 +2066,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>90500</v>
+        <v>7800</v>
       </c>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
@@ -2061,7 +2079,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2070,43 +2088,53 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1248.47</v>
+      </c>
       <c r="H20" t="n">
-        <v>1538.51</v>
+        <v>1477.65</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30.62%</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>55.61%</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23.33%</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>21.08%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>14.42%</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2122억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2115,12 +2143,24 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>7800</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>42750</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>256.25%</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>45700</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>6.90%</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -2128,7 +2168,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2137,53 +2177,53 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1248.47</v>
+        <v>50.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1477.65</v>
+        <v>3.09</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>55.61%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21.08%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>14.42%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1202억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2195,19 +2235,19 @@
         <v>12000</v>
       </c>
       <c r="P21" t="n">
-        <v>42750</v>
+        <v>10960</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>256.25%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="R21" t="n">
-        <v>45700</v>
+        <v>17990</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>6.90%</t>
+          <t>64.14%</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2217,7 +2257,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2226,79 +2266,67 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>50.4</v>
+        <v>1097.62</v>
       </c>
       <c r="H22" t="n">
-        <v>3.09</v>
+        <v>685.33</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>5.29%</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>72.75%</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>25.60%</t>
+          <t>58.44%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25.36%</t>
+          <t>46.16%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>890억</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P22" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R22" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+        <v>23500</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2306,76 +2334,62 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1097.62</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>685.33</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5.29%</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>72.75%</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>58.44%</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>46.16%</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>890억</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>유</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>1905</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-52.37%</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
@@ -2383,224 +2397,250 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H24" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O24" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="P24" t="n">
-        <v>4000</v>
+        <v>21000</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>90.91%</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>1905</v>
+        <v>15380</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-52.37%</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P25" t="n">
-        <v>21000</v>
+        <v>3415</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>70.75%</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>15380</v>
+        <v>1937</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-43.28%</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>101.91</v>
+      </c>
       <c r="H26" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+        <v>25.73</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O26" t="n">
-        <v>2000</v>
+        <v>23000</v>
       </c>
       <c r="P26" t="n">
-        <v>3415</v>
+        <v>20500</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>70.75%</t>
+          <t>-10.87%</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>1937</v>
+        <v>13930</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>-43.28%</t>
+          <t>-32.05%</t>
         </is>
       </c>
       <c r="T26" t="inlineStr"/>
@@ -2608,95 +2648,6 @@
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>14</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>해치텍</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>반도체 제조업</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>DB증권</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="H27" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P27" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -2041,20 +2041,28 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1538.51</v>
+        <v>1542.36</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>30.62%</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>82.52%</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>23.33%</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>14.72%</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>2122억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1408,10 +1408,22 @@
       <c r="O11" t="n">
         <v>12300</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>27400</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>122.76%</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>17120</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>-37.52%</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>27450.0</t>
@@ -2041,7 +2053,7 @@
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>1542.36</v>
+        <v>1538.51</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2331,10 +2343,22 @@
       <c r="O22" t="n">
         <v>23500</v>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>24000</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>14350</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-40.21%</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1013,20 +1013,28 @@
         <v>983.98</v>
       </c>
       <c r="H7" t="n">
-        <v>986.9400000000001</v>
+        <v>986.89</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>13.31%</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>61.00%</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>15.12%</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>8.27%</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>2753억</t>
@@ -1762,7 +1770,9 @@
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>656.02</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1013,7 +1013,7 @@
         <v>983.98</v>
       </c>
       <c r="H7" t="n">
-        <v>986.89</v>
+        <v>986.9400000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2540,62 +2540,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
+          <t>삼성증권</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
-        <v>494.62</v>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>39.47%</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P25" t="n">
-        <v>3415</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>70.75%</t>
-        </is>
-      </c>
-      <c r="R25" t="n">
-        <v>1937</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -2603,7 +2591,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2612,84 +2600,261 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>신한투자증권, 신한투자증권와</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="H26" t="n">
-        <v>25.73</v>
-      </c>
+        <v>1041.02</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
+          <t>95.20%</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
+          <t>31.29%</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1271억</t>
+          <t>1737억</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P26" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R26" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
+        <v>15300</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>스펙</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>금융 지원 서비스업</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>494.62</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3415</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>70.75%</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>1937</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>-43.28%</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>28</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>스펙</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화플러스제6호스팩</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>14</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H29" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P29" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W29"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2562,24 +2562,34 @@
           <t>삼성증권</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>39.47%</t>
+          <t>39.43%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1970억</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>유</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O25" t="n">
+        <v>15000</v>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
@@ -2591,7 +2601,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2600,52 +2610,46 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>일반 목적용 기계 제조업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>신한투자증권, 신한투자증권와</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>1041.02</v>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>95.20%</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>31.29%</t>
+          <t>39.43%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1737억</t>
+          <t>1970억</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>15300</v>
+        <v>15000</v>
       </c>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -2658,62 +2662,66 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>신한투자증권, 신한투자증권와</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1041.02</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>95.20%</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>31.29%</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>1737억</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O27" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P27" t="n">
-        <v>3415</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>70.75%</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>1937</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
+        <v>15300</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
@@ -2721,7 +2729,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2730,37 +2738,53 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>한화투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>494.62</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P28" t="n">
+        <v>3415</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>70.75%</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>1937</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>-43.28%</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
@@ -2768,93 +2792,142 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한화투자증권</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="H29" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P29" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R29" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>14</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H30" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P30" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -2287,7 +2287,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2296,79 +2296,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>하나증권</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>1097.62</v>
-      </c>
-      <c r="H22" t="n">
-        <v>685.33</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5.29%</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>72.75%</t>
-        </is>
-      </c>
+          <t>미래에셋증권</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>58.44%</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>46.16%</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>890억</t>
-        </is>
-      </c>
+          <t>23.95%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>유</t>
         </is>
       </c>
-      <c r="O22" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P22" t="n">
-        <v>24000</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>2.13%</t>
-        </is>
-      </c>
-      <c r="R22" t="n">
-        <v>14350</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>-40.21%</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2376,60 +2338,86 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1097.62</v>
+      </c>
       <c r="H23" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+        <v>685.33</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>72.75%</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>58.44%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>46.16%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>890억</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O23" t="n">
-        <v>2000</v>
+        <v>23500</v>
       </c>
       <c r="P23" t="n">
-        <v>4000</v>
+        <v>24000</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="R23" t="n">
-        <v>1905</v>
+        <v>14350</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>-52.37%</t>
+          <t>-40.21%</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2439,108 +2427,70 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P24" t="n">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>15380</v>
+        <v>1905</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-52.37%</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2549,37 +2499,53 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>그외 기타 제품 제조업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>39.43%</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1970억</t>
+          <t>1129억</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2588,15 +2554,39 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>15000</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P25" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W30"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1771,16 +1771,24 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>656.02</v>
+        <v>1</v>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14.83%</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>97.45%</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>86.61%</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>133억</t>
@@ -2309,8 +2317,14 @@
           <t>미래에셋증권</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1234.3</v>
+      </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
@@ -2320,13 +2334,19 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>1020억</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>유</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>9000</v>
+      </c>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
@@ -2338,7 +2358,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2347,79 +2367,53 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1097.62</v>
-      </c>
-      <c r="H23" t="n">
-        <v>685.33</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>5.29%</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>72.75%</t>
-        </is>
-      </c>
+        <v>1234.3</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>58.44%</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>46.16%</t>
-        </is>
-      </c>
+          <t>23.95%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>890억</t>
+          <t>1020억</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P23" t="n">
-        <v>24000</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2.13%</t>
-        </is>
-      </c>
-      <c r="R23" t="n">
-        <v>14350</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>-40.21%</t>
-        </is>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
@@ -2427,60 +2421,86 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1097.62</v>
+      </c>
       <c r="H24" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+        <v>685.33</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>72.75%</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>58.44%</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>46.16%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>890억</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O24" t="n">
-        <v>2000</v>
+        <v>23500</v>
       </c>
       <c r="P24" t="n">
-        <v>4000</v>
+        <v>24000</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>1905</v>
+        <v>14350</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-52.37%</t>
+          <t>-40.21%</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2490,108 +2510,70 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P25" t="n">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R25" t="n">
-        <v>15380</v>
+        <v>1905</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-52.37%</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2600,37 +2582,53 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>그외 기타 제품 제조업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>938.24</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>39.43%</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1970억</t>
+          <t>1129억</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2639,20 +2637,44 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>15000</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P26" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2661,52 +2683,46 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>일반 목적용 기계 제조업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>신한투자증권, 신한투자증권와</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1041.02</v>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>95.20%</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>31.29%</t>
+          <t>39.43%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>1737억</t>
+          <t>1970억</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>15300</v>
+        <v>15000</v>
       </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -2719,62 +2735,66 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>신한투자증권, 신한투자증권와</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>1041.02</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>95.20%</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>31.29%</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>1737억</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P28" t="n">
-        <v>3415</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>70.75%</t>
-        </is>
-      </c>
-      <c r="R28" t="n">
-        <v>1937</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
+        <v>15300</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
@@ -2782,7 +2802,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2791,26 +2811,28 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>한화투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>494.62</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -2820,10 +2842,22 @@
       <c r="O29" t="n">
         <v>2000</v>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>3415</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>70.75%</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>1937</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-43.28%</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2831,93 +2865,142 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한화투자증권</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="H30" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P30" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R30" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>14</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H31" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P31" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,7 +1148,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1157,99 +1157,55 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KB증권</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1146.41</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1706.71</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>17.93%</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>77.50%</t>
-        </is>
-      </c>
+          <t>NH투자증권</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>41.03%</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>31.89%</t>
-        </is>
-      </c>
+          <t>35.57%</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1579억</t>
+          <t>2763억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>20700</v>
-      </c>
-      <c r="P9" t="n">
-        <v>30750</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>48.55%</t>
-        </is>
-      </c>
-      <c r="R9" t="n">
-        <v>22000</v>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>-28.46%</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>31000.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>49.76%</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>51190.0</t>
-        </is>
-      </c>
+        <v>19000</v>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1258,12 +1214,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1273,38 +1229,38 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1238</v>
+        <v>1146.41</v>
       </c>
       <c r="H10" t="n">
-        <v>1510.57</v>
+        <v>1706.71</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>17.93%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>77.50%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>41.03%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>31.89%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1313,44 +1269,44 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>10000</v>
+        <v>20700</v>
       </c>
       <c r="P10" t="n">
-        <v>16560</v>
+        <v>30750</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>65.60%</t>
+          <t>48.55%</t>
         </is>
       </c>
       <c r="R10" t="n">
-        <v>9400</v>
+        <v>22000</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-43.24%</t>
+          <t>-28.46%</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>18740.0</t>
+          <t>31000.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>87.40%</t>
+          <t>49.76%</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>69621.0</t>
+          <t>51190.0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1359,53 +1315,53 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1136.84</v>
+        <v>1238</v>
       </c>
       <c r="H11" t="n">
-        <v>1741.48</v>
+        <v>1510.57</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>36.07%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>73.94%</t>
+          <t>74.17%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>34.50%</t>
+          <t>33.19%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>23.79%</t>
+          <t>24.86%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1550억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1414,44 +1370,44 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>12300</v>
+        <v>10000</v>
       </c>
       <c r="P11" t="n">
-        <v>27400</v>
+        <v>16560</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>122.76%</t>
+          <t>65.60%</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>17120</v>
+        <v>9400</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-37.52%</t>
+          <t>-43.24%</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>27450.0</t>
+          <t>18740.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>123.17%</t>
+          <t>87.40%</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>180493.0</t>
+          <t>69621.0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1460,7 +1416,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1470,43 +1426,43 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1187.74</v>
+        <v>1136.84</v>
       </c>
       <c r="H12" t="n">
-        <v>1676.26</v>
+        <v>1741.48</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>21.75%</t>
+          <t>36.07%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>85.39%</t>
+          <t>73.94%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>34.50%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>21.01%</t>
+          <t>23.79%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1875억</t>
+          <t>1550억</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1515,44 +1471,44 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>16500</v>
+        <v>12300</v>
       </c>
       <c r="P12" t="n">
-        <v>61800</v>
+        <v>27400</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>274.55%</t>
+          <t>122.76%</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>31100</v>
+        <v>17120</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-49.68%</t>
+          <t>-37.52%</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>61100.0</t>
+          <t>27450.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>270.30%</t>
+          <t>123.17%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>332800.0</t>
+          <t>180493.0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1561,99 +1517,99 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>유진투자증권, 미래에셋증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1109.37</v>
+        <v>1187.74</v>
       </c>
       <c r="H13" t="n">
-        <v>1375.08</v>
+        <v>1676.26</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>98.72%</t>
+          <t>21.75%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>78.39%</t>
+          <t>85.39%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>26.76%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>18.35%</t>
+          <t>21.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1849억</t>
+          <t>1875억</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>18000</v>
+        <v>16500</v>
       </c>
       <c r="P13" t="n">
-        <v>56000</v>
+        <v>61800</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>211.11%</t>
+          <t>274.55%</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>27050</v>
+        <v>31100</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-51.70%</t>
+          <t>-49.68%</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>52300.0</t>
+          <t>61100.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>190.56%</t>
+          <t>270.30%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>307743.0</t>
+          <t>332800.0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1662,87 +1618,99 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>63.41</v>
+        <v>1109.37</v>
       </c>
       <c r="H14" t="n">
-        <v>2.85</v>
+        <v>1375.08</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>98.72%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>78.39%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>27.26%</t>
+          <t>26.76%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>18.35%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1876억</t>
+          <t>1849억</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="P14" t="n">
-        <v>8500</v>
+        <v>56000</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-15.00%</t>
+          <t>211.11%</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>23500</v>
+        <v>27050</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>176.47%</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+          <t>-51.70%</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>52300.0</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>190.56%</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>307743.0</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1751,47 +1719,53 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>63.41</v>
+      </c>
       <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+        <v>2.85</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14.83%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>97.45%</t>
+          <t>27.26%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>86.61%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>133억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1800,12 +1774,24 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8500</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>-15.00%</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>23500</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>176.47%</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
@@ -1813,7 +1799,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1822,53 +1808,47 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>714.52</v>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>666.78</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
+        <v>656.02</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>14.83%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>97.45%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>86.61%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>133억</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1877,24 +1857,12 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>21500</v>
-      </c>
-      <c r="P16" t="n">
-        <v>21500</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>14790</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>-31.21%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1902,60 +1870,86 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H17" t="n">
-        <v>357</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O17" t="n">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="P17" t="n">
-        <v>4000</v>
+        <v>21500</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R17" t="n">
-        <v>2075</v>
+        <v>14790</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -1965,76 +1959,62 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>388.84</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>408.16</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>13.70%</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>31.33%</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>20.77%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>16.08%</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>10072억</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>90500</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>2075</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-48.12%</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
@@ -2042,7 +2022,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2051,51 +2031,53 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>388.84</v>
+      </c>
       <c r="H19" t="n">
-        <v>1538.51</v>
+        <v>408.16</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30.62%</t>
+          <t>13.70%</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>82.52%</t>
+          <t>31.33%</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>23.33%</t>
+          <t>20.77%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>14.72%</t>
+          <t>16.08%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2122억</t>
+          <t>10072억</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2104,12 +2086,24 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>7800</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+        <v>90500</v>
+      </c>
+      <c r="P19" t="n">
+        <v>75700</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>-16.35%</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>61600</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>-18.63%</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
@@ -2117,7 +2111,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2126,53 +2120,51 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>1248.47</v>
-      </c>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>1477.65</v>
+        <v>1538.51</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>30.62%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>55.61%</t>
+          <t>82.52%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>21.08%</t>
+          <t>23.33%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>14.42%</t>
+          <t>14.72%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1202억</t>
+          <t>2122억</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2181,24 +2173,12 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P20" t="n">
-        <v>42750</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>256.25%</t>
-        </is>
-      </c>
-      <c r="R20" t="n">
-        <v>45700</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>6.90%</t>
-        </is>
-      </c>
+        <v>7800</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -2206,7 +2186,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2215,79 +2195,47 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>삼성증권</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
+          <t>31.75%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1537억</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P21" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R21" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+        <v>17000</v>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -2295,7 +2243,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2304,39 +2252,53 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1234.3</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+        <v>1248.47</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1477.65</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>55.61%</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23.95%</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>21.08%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>14.42%</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1020억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2345,12 +2307,24 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>9000</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>42750</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>256.25%</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>45700</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>6.90%</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2358,7 +2332,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2367,49 +2341,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1234.3</v>
-      </c>
+          <t>대신증권</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23.95%</t>
+          <t>37.70%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>1020억</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>9000</v>
-      </c>
+          <t>유</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -2421,7 +2383,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2430,77 +2392,77 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1097.62</v>
+        <v>50.4</v>
       </c>
       <c r="H24" t="n">
-        <v>685.33</v>
+        <v>3.09</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>72.75%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>58.44%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>46.16%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>890억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>23500</v>
+        <v>12000</v>
       </c>
       <c r="P24" t="n">
-        <v>24000</v>
+        <v>10960</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>14350</v>
+        <v>17990</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>-40.21%</t>
+          <t>64.14%</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2510,62 +2472,62 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="n">
-        <v>397.33</v>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1234.3</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>23.95%</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>1020억</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O25" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P25" t="n">
-        <v>4000</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="R25" t="n">
-        <v>1905</v>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>-52.37%</t>
-        </is>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -2573,7 +2535,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2582,152 +2544,142 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>938.24</v>
+        <v>1097.62</v>
       </c>
       <c r="H26" t="n">
-        <v>1079.55</v>
+        <v>685.33</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>5.29%</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>71.42%</t>
+          <t>72.75%</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>30.03%</t>
+          <t>58.44%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>17.59%</t>
+          <t>46.16%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1129억</t>
+          <t>890억</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>11000</v>
+        <v>23500</v>
       </c>
       <c r="P26" t="n">
-        <v>21000</v>
+        <v>24000</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="R26" t="n">
-        <v>15380</v>
+        <v>14350</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-40.21%</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>그외 기타 제품 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>397.33</v>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>39.43%</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>1970억</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>15000</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="P27" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>1905</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>-52.37%</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
@@ -2735,7 +2687,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2744,120 +2696,152 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>일반 목적용 기계 제조업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>신한투자증권, 신한투자증권와</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1041.02</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>938.24</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1079.55</v>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>95.20%</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>31.29%</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1737억</t>
+          <t>1129억</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>15300</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P28" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="n">
-        <v>494.62</v>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>39.43%</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>1970억</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O29" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P29" t="n">
-        <v>3415</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>70.75%</t>
-        </is>
-      </c>
-      <c r="R29" t="n">
-        <v>1937</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
+        <v>15000</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2865,43 +2849,61 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>한화투자증권</t>
+          <t>신한투자증권, 신한투자증권와</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1041.02</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>95.20%</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>31.29%</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1737억</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O30" t="n">
-        <v>2000</v>
+        <v>15300</v>
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -2914,86 +2916,60 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>101.91</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="P31" t="n">
-        <v>20500</v>
+        <v>3415</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>-10.87%</t>
+          <t>70.75%</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>13930</v>
+        <v>1937</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>-32.05%</t>
+          <t>-43.28%</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3001,6 +2977,144 @@
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>스펙</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화플러스제6호스팩</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>14</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H33" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P33" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W33"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1170,25 +1170,31 @@
           <t>NH투자증권</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-11-03</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>284.53</v>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>35.57%</t>
+          <t>35.51%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2763억</t>
+          <t>2768억</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1205,7 +1211,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1214,53 +1220,39 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-11-03</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1146.41</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1706.71</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>17.93%</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>77.50%</t>
-        </is>
-      </c>
+        <v>284.53</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>41.03%</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>31.89%</t>
-        </is>
-      </c>
+          <t>35.51%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1579억</t>
+          <t>2768억</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1269,44 +1261,20 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>20700</v>
-      </c>
-      <c r="P10" t="n">
-        <v>30750</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>48.55%</t>
-        </is>
-      </c>
-      <c r="R10" t="n">
-        <v>22000</v>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>-28.46%</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>31000.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>49.76%</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>51190.0</t>
-        </is>
-      </c>
+        <v>19000</v>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1315,12 +1283,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1330,38 +1298,38 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1238</v>
+        <v>1146.41</v>
       </c>
       <c r="H11" t="n">
-        <v>1510.57</v>
+        <v>1706.71</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>17.93%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>77.50%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>41.03%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>31.89%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1370,44 +1338,44 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>10000</v>
+        <v>20700</v>
       </c>
       <c r="P11" t="n">
-        <v>16560</v>
+        <v>30750</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>65.60%</t>
+          <t>48.55%</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>9400</v>
+        <v>22000</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-43.24%</t>
+          <t>-28.46%</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>18740.0</t>
+          <t>31000.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>87.40%</t>
+          <t>49.76%</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>69621.0</t>
+          <t>51190.0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1416,53 +1384,53 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1136.84</v>
+        <v>1238</v>
       </c>
       <c r="H12" t="n">
-        <v>1741.48</v>
+        <v>1510.57</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>36.07%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>73.94%</t>
+          <t>74.17%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>34.50%</t>
+          <t>33.19%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>23.79%</t>
+          <t>24.86%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1550억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1471,44 +1439,44 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>12300</v>
+        <v>10000</v>
       </c>
       <c r="P12" t="n">
-        <v>27400</v>
+        <v>16560</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>122.76%</t>
+          <t>65.60%</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>17120</v>
+        <v>9400</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-37.52%</t>
+          <t>-43.24%</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>27450.0</t>
+          <t>18740.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>123.17%</t>
+          <t>87.40%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>180493.0</t>
+          <t>69621.0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1517,7 +1485,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1527,43 +1495,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1187.74</v>
+        <v>1136.84</v>
       </c>
       <c r="H13" t="n">
-        <v>1676.26</v>
+        <v>1741.48</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21.75%</t>
+          <t>36.07%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>85.39%</t>
+          <t>73.94%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>34.50%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>21.01%</t>
+          <t>23.79%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1875억</t>
+          <t>1550억</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1572,44 +1540,44 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>16500</v>
+        <v>12300</v>
       </c>
       <c r="P13" t="n">
-        <v>61800</v>
+        <v>27400</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>274.55%</t>
+          <t>122.76%</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>31100</v>
+        <v>17120</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-49.68%</t>
+          <t>-37.52%</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>61100.0</t>
+          <t>27450.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>270.30%</t>
+          <t>123.17%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>332800.0</t>
+          <t>180493.0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1618,99 +1586,99 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>유진투자증권, 미래에셋증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1109.37</v>
+        <v>1187.74</v>
       </c>
       <c r="H14" t="n">
-        <v>1375.08</v>
+        <v>1676.26</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>98.72%</t>
+          <t>21.75%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>78.39%</t>
+          <t>85.39%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>26.76%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>18.35%</t>
+          <t>21.01%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1849억</t>
+          <t>1875억</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>18000</v>
+        <v>16500</v>
       </c>
       <c r="P14" t="n">
-        <v>56000</v>
+        <v>61800</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>211.11%</t>
+          <t>274.55%</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>27050</v>
+        <v>31100</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-51.70%</t>
+          <t>-49.68%</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>52300.0</t>
+          <t>61100.0</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>190.56%</t>
+          <t>270.30%</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>307743.0</t>
+          <t>332800.0</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1719,87 +1687,99 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>63.41</v>
+        <v>1109.37</v>
       </c>
       <c r="H15" t="n">
-        <v>2.85</v>
+        <v>1375.08</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>98.72%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>78.39%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>27.26%</t>
+          <t>26.76%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>18.35%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1876억</t>
+          <t>1849억</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>10000</v>
+        <v>18000</v>
       </c>
       <c r="P15" t="n">
-        <v>8500</v>
+        <v>56000</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-15.00%</t>
+          <t>211.11%</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>23500</v>
+        <v>27050</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>176.47%</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+          <t>-51.70%</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>52300.0</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>190.56%</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>307743.0</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1808,47 +1788,53 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>63.41</v>
+      </c>
       <c r="H16" t="n">
-        <v>656.02</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>2.85</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14.83%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>97.45%</t>
+          <t>27.26%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>86.61%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>133억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1857,12 +1843,24 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+        <v>10000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>8500</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>-15.00%</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>23500</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>176.47%</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1870,7 +1868,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1879,53 +1877,47 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>714.52</v>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>666.78</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
+        <v>656.02</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>14.83%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>97.45%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>86.61%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>133억</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1934,24 +1926,12 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>21500</v>
-      </c>
-      <c r="P17" t="n">
-        <v>21500</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>14790</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>-31.21%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1959,60 +1939,86 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H18" t="n">
-        <v>357</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="P18" t="n">
-        <v>4000</v>
+        <v>21500</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2075</v>
+        <v>14790</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2022,86 +2028,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>388.84</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>408.16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13.70%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>31.33%</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>20.77%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>16.08%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>10072억</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>90500</v>
+        <v>2000</v>
       </c>
       <c r="P19" t="n">
-        <v>75700</v>
+        <v>4000</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-16.35%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>61600</v>
+        <v>2075</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-18.63%</t>
+          <t>-48.12%</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2111,7 +2091,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2120,51 +2100,53 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>388.84</v>
+      </c>
       <c r="H20" t="n">
-        <v>1538.51</v>
+        <v>408.16</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30.62%</t>
+          <t>13.70%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>82.52%</t>
+          <t>31.33%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23.33%</t>
+          <t>20.77%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>14.72%</t>
+          <t>16.08%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2122억</t>
+          <t>10072억</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2173,12 +2155,24 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>7800</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+        <v>90500</v>
+      </c>
+      <c r="P20" t="n">
+        <v>75700</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>-16.35%</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>61600</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-18.63%</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -2186,7 +2180,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2195,42 +2189,60 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>KB증권</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>1538.51</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30.62%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>82.52%</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31.75%</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>23.33%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>14.72%</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1537억</t>
+          <t>2122억</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>17000</v>
+        <v>7800</v>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -2243,7 +2255,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2252,53 +2264,43 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1248.47</v>
-      </c>
-      <c r="H22" t="n">
-        <v>1477.65</v>
-      </c>
+        <v>1000.07</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.65%</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>55.61%</t>
-        </is>
-      </c>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21.08%</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>14.42%</t>
-        </is>
-      </c>
+          <t>31.75%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1202억</t>
+          <t>1537억</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2307,24 +2309,12 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P22" t="n">
-        <v>42750</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>256.25%</t>
-        </is>
-      </c>
-      <c r="R22" t="n">
-        <v>45700</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>6.90%</t>
-        </is>
-      </c>
+        <v>17000</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2332,7 +2322,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2341,37 +2331,53 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>대신증권</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1000.07</v>
+      </c>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0.87%</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>37.70%</t>
+          <t>31.75%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1537억</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>유</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>17000</v>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -2383,7 +2389,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2392,53 +2398,53 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>50.4</v>
+        <v>1248.47</v>
       </c>
       <c r="H24" t="n">
-        <v>3.09</v>
+        <v>1477.65</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>55.61%</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>25.60%</t>
+          <t>21.08%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>25.36%</t>
+          <t>14.42%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2450,19 +2456,19 @@
         <v>12000</v>
       </c>
       <c r="P24" t="n">
-        <v>10960</v>
+        <v>42750</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>256.25%</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>17990</v>
+        <v>45700</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>64.14%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2472,7 +2478,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2481,39 +2487,43 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1234.3</v>
+        <v>630.1</v>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>23.95%</t>
+          <t>37.62%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1020억</t>
+          <t>1728억</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2522,7 +2532,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>9000</v>
+        <v>12400</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
@@ -2535,7 +2545,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2544,79 +2554,57 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1097.62</v>
-      </c>
-      <c r="H26" t="n">
-        <v>685.33</v>
-      </c>
+        <v>630.1</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5.29%</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>72.75%</t>
-        </is>
-      </c>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>58.44%</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>46.16%</t>
-        </is>
-      </c>
+          <t>37.62%</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>890억</t>
+          <t>1728억</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P26" t="n">
-        <v>24000</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>2.13%</t>
-        </is>
-      </c>
-      <c r="R26" t="n">
-        <v>14350</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>-40.21%</t>
-        </is>
-      </c>
+        <v>12400</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
@@ -2624,60 +2612,86 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>50.4</v>
+      </c>
       <c r="H27" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+        <v>3.09</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>5933억</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O27" t="n">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="P27" t="n">
-        <v>4000</v>
+        <v>10960</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>1905</v>
+        <v>17990</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>-52.37%</t>
+          <t>64.14%</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -2687,7 +2701,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2696,53 +2710,39 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>938.24</v>
-      </c>
-      <c r="H28" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
+        <v>1234.3</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
+          <t>23.95%</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1129억</t>
+          <t>1020억</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2751,44 +2751,20 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>11000</v>
-      </c>
-      <c r="P28" t="n">
-        <v>21000</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>90.91%</t>
-        </is>
-      </c>
-      <c r="R28" t="n">
-        <v>15380</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2797,51 +2773,79 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>그외 기타 제품 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1097.62</v>
+      </c>
+      <c r="H29" t="n">
+        <v>685.33</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>72.75%</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>39.43%</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+          <t>58.44%</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>46.16%</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1970억</t>
+          <t>890억</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>15000</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+        <v>23500</v>
+      </c>
+      <c r="P29" t="n">
+        <v>24000</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>14350</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-40.21%</t>
+        </is>
+      </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2849,66 +2853,62 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>일반 목적용 기계 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>신한투자증권, 신한투자증권와</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1041.02</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>95.20%</t>
-        </is>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>397.33</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>31.29%</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>1737억</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>유</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>15300</v>
-      </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+        <v>2000</v>
+      </c>
+      <c r="P30" t="n">
+        <v>4000</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>1905</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>-52.37%</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
@@ -2916,89 +2916,127 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H31" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1129억</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O31" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="P31" t="n">
-        <v>3415</v>
+        <v>21000</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>70.75%</t>
+          <t>90.91%</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>1937</v>
+        <v>15380</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>한화투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3007,15 +3045,29 @@
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>6.92</v>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>39.43%</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>1970억</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O32" t="n">
-        <v>2000</v>
+        <v>15000</v>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -3028,7 +3080,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3037,84 +3089,267 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>신한투자증권, 신한투자증권와</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>101.91</v>
+        <v>1041.02</v>
       </c>
       <c r="H33" t="n">
-        <v>25.73</v>
+        <v>1252.9</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
+          <t>95.20%</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
+          <t>31.29%</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1271억</t>
+          <t>1737억</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P33" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
+        <v>15300</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>13</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>스펙</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>금융 지원 서비스업</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>494.62</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P34" t="n">
+        <v>3415</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>70.75%</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>1937</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>-43.28%</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>스펙</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화플러스제6호스팩</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화투자증권</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>14</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H36" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P36" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:W33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,7 +1211,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1220,39 +1220,53 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-11-03</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>284.53</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+        <v>1146.41</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1706.71</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>17.93%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>77.50%</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>35.51%</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>41.03%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>31.89%</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2768억</t>
+          <t>1579억</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1261,20 +1275,44 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>19000</v>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
+        <v>20700</v>
+      </c>
+      <c r="P10" t="n">
+        <v>30750</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>48.55%</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>22000</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>-28.46%</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>31000.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>49.76%</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>51190.0</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1283,12 +1321,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1298,38 +1336,38 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1146.41</v>
+        <v>1238</v>
       </c>
       <c r="H11" t="n">
-        <v>1706.71</v>
+        <v>1510.57</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17.93%</t>
+          <t>6.92%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.50%</t>
+          <t>74.17%</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>41.03%</t>
+          <t>33.19%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31.89%</t>
+          <t>24.86%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1579억</t>
+          <t>1335억</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1338,44 +1376,44 @@
         </is>
       </c>
       <c r="O11" t="n">
-        <v>20700</v>
+        <v>10000</v>
       </c>
       <c r="P11" t="n">
-        <v>30750</v>
+        <v>16560</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>48.55%</t>
+          <t>65.60%</t>
         </is>
       </c>
       <c r="R11" t="n">
-        <v>22000</v>
+        <v>9400</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-28.46%</t>
+          <t>-43.24%</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>31000.0</t>
+          <t>18740.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>49.76%</t>
+          <t>87.40%</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>51190.0</t>
+          <t>69621.0</t>
         </is>
       </c>
       <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1384,53 +1422,53 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1238</v>
+        <v>1136.84</v>
       </c>
       <c r="H12" t="n">
-        <v>1510.57</v>
+        <v>1741.48</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6.92%</t>
+          <t>36.07%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>74.17%</t>
+          <t>73.94%</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>33.19%</t>
+          <t>34.50%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>24.86%</t>
+          <t>23.79%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1335억</t>
+          <t>1550억</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1439,44 +1477,44 @@
         </is>
       </c>
       <c r="O12" t="n">
-        <v>10000</v>
+        <v>12300</v>
       </c>
       <c r="P12" t="n">
-        <v>16560</v>
+        <v>27400</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>65.60%</t>
+          <t>122.76%</t>
         </is>
       </c>
       <c r="R12" t="n">
-        <v>9400</v>
+        <v>17120</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>-43.24%</t>
+          <t>-37.52%</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>18740.0</t>
+          <t>27450.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>87.40%</t>
+          <t>123.17%</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>69621.0</t>
+          <t>180493.0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1485,7 +1523,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1495,43 +1533,43 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1136.84</v>
+        <v>1187.74</v>
       </c>
       <c r="H13" t="n">
-        <v>1741.48</v>
+        <v>1676.26</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>36.07%</t>
+          <t>21.75%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>73.94%</t>
+          <t>85.39%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>34.50%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23.79%</t>
+          <t>21.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1550억</t>
+          <t>1875억</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1540,44 +1578,44 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>12300</v>
+        <v>16500</v>
       </c>
       <c r="P13" t="n">
-        <v>27400</v>
+        <v>61800</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>122.76%</t>
+          <t>274.55%</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>17120</v>
+        <v>31100</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>-37.52%</t>
+          <t>-49.68%</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>27450.0</t>
+          <t>61100.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>123.17%</t>
+          <t>270.30%</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>180493.0</t>
+          <t>332800.0</t>
         </is>
       </c>
       <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1586,99 +1624,99 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>유진투자증권, 미래에셋증권</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1187.74</v>
+        <v>1109.37</v>
       </c>
       <c r="H14" t="n">
-        <v>1676.26</v>
+        <v>1375.08</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21.75%</t>
+          <t>98.72%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>85.39%</t>
+          <t>78.39%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>26.76%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>21.01%</t>
+          <t>18.35%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1875억</t>
+          <t>1849억</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>16500</v>
+        <v>18000</v>
       </c>
       <c r="P14" t="n">
-        <v>61800</v>
+        <v>56000</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>274.55%</t>
+          <t>211.11%</t>
         </is>
       </c>
       <c r="R14" t="n">
-        <v>31100</v>
+        <v>27050</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>-49.68%</t>
+          <t>-51.70%</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>61100.0</t>
+          <t>52300.0</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>270.30%</t>
+          <t>190.56%</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>332800.0</t>
+          <t>307743.0</t>
         </is>
       </c>
       <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1687,99 +1725,87 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>유진투자증권, 미래에셋증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1109.37</v>
+        <v>63.41</v>
       </c>
       <c r="H15" t="n">
-        <v>1375.08</v>
+        <v>2.85</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>98.72%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>78.39%</t>
+          <t>10.93%</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>26.76%</t>
+          <t>27.26%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>18.35%</t>
+          <t>26.42%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1849억</t>
+          <t>1876억</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="P15" t="n">
-        <v>56000</v>
+        <v>8500</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>211.11%</t>
+          <t>-15.00%</t>
         </is>
       </c>
       <c r="R15" t="n">
-        <v>27050</v>
+        <v>23500</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>-51.70%</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>52300.0</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>190.56%</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>307743.0</t>
-        </is>
-      </c>
+          <t>176.47%</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1788,53 +1814,47 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>63.41</v>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.17%</t>
-        </is>
-      </c>
+        <v>656.02</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>10.93%</t>
+          <t>14.83%</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>27.26%</t>
+          <t>97.45%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>26.42%</t>
+          <t>86.61%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1876억</t>
+          <t>133억</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1843,24 +1863,12 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="P16" t="n">
-        <v>8500</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>-15.00%</t>
-        </is>
-      </c>
-      <c r="R16" t="n">
-        <v>23500</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>176.47%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
@@ -1868,7 +1876,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1877,47 +1885,53 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H17" t="n">
-        <v>656.02</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.83%</t>
+          <t>34.58%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>97.45%</t>
+          <t>33.00%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>86.61%</t>
+          <t>24.41%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>133억</t>
+          <t>1673억</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1926,12 +1940,24 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+        <v>21500</v>
+      </c>
+      <c r="P17" t="n">
+        <v>21500</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>14790</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-31.21%</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1939,86 +1965,60 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>714.52</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>666.78</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>34.58%</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>33.00%</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>24.41%</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>1673억</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>21500</v>
+        <v>2000</v>
       </c>
       <c r="P18" t="n">
-        <v>21500</v>
+        <v>4000</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>14790</v>
+        <v>2075</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-31.21%</t>
+          <t>-48.12%</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2028,60 +2028,86 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>388.84</v>
+      </c>
       <c r="H19" t="n">
-        <v>357</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+        <v>408.16</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>13.70%</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>31.33%</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>20.77%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>16.08%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>10072억</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O19" t="n">
-        <v>2000</v>
+        <v>90500</v>
       </c>
       <c r="P19" t="n">
-        <v>4000</v>
+        <v>75700</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>-16.35%</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>2075</v>
+        <v>61600</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-18.63%</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2091,7 +2117,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2100,53 +2126,51 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>388.84</v>
-      </c>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>408.16</v>
+        <v>1538.51</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>13.70%</t>
+          <t>30.62%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>31.33%</t>
+          <t>82.52%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>20.77%</t>
+          <t>23.33%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>16.08%</t>
+          <t>14.72%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>10072억</t>
+          <t>2122억</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2155,24 +2179,12 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>90500</v>
-      </c>
-      <c r="P20" t="n">
-        <v>75700</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>-16.35%</t>
-        </is>
-      </c>
-      <c r="R20" t="n">
-        <v>61600</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>-18.63%</t>
-        </is>
-      </c>
+        <v>7800</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
@@ -2180,7 +2192,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2189,51 +2201,43 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="n">
-        <v>1538.51</v>
-      </c>
+          <t>2026-11-02</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1000.07</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30.62%</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>82.52%</t>
-        </is>
-      </c>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>23.33%</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>14.72%</t>
-        </is>
-      </c>
+          <t>31.75%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2122억</t>
+          <t>1537억</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2242,7 +2246,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>7800</v>
+        <v>17000</v>
       </c>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -2255,7 +2259,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2264,43 +2268,53 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1000.07</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>1248.47</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1477.65</v>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.87%</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>55.61%</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31.75%</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>21.08%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>14.42%</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1537억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2309,12 +2323,24 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>17000</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>42750</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>256.25%</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>45700</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>6.90%</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2322,7 +2348,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2331,43 +2357,43 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1000.07</v>
+        <v>630.1</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.24%</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>31.75%</t>
+          <t>37.62%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1537억</t>
+          <t>1728억</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2376,7 +2402,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>17000</v>
+        <v>12400</v>
       </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
@@ -2389,7 +2415,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2398,53 +2424,53 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1248.47</v>
+        <v>50.4</v>
       </c>
       <c r="H24" t="n">
-        <v>1477.65</v>
+        <v>3.09</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.65%</t>
+          <t>2.23%</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>55.61%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>21.08%</t>
+          <t>25.60%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>14.42%</t>
+          <t>25.36%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1202억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2456,19 +2482,19 @@
         <v>12000</v>
       </c>
       <c r="P24" t="n">
-        <v>42750</v>
+        <v>10960</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>256.25%</t>
+          <t>-8.67%</t>
         </is>
       </c>
       <c r="R24" t="n">
-        <v>45700</v>
+        <v>17990</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>6.90%</t>
+          <t>64.14%</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2478,7 +2504,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2487,43 +2513,39 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>630.1</v>
+        <v>1234.3</v>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>37.62%</t>
+          <t>23.95%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1728억</t>
+          <t>1020억</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2532,7 +2554,7 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>12400</v>
+        <v>9000</v>
       </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
@@ -2545,7 +2567,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2554,57 +2576,79 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>630.1</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>1097.62</v>
+      </c>
+      <c r="H26" t="n">
+        <v>685.33</v>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>72.75%</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>37.62%</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>58.44%</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>46.16%</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>1728억</t>
+          <t>890억</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>무</t>
+          <t>유</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>12400</v>
-      </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+        <v>23500</v>
+      </c>
+      <c r="P26" t="n">
+        <v>24000</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2.13%</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>14350</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-40.21%</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
@@ -2612,86 +2656,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>50.4</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>5933억</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="n">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="P27" t="n">
-        <v>10960</v>
+        <v>4000</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-8.67%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>17990</v>
+        <v>1905</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>64.14%</t>
+          <t>-52.37%</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -2701,7 +2719,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2710,39 +2728,53 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1234.3</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+        <v>938.24</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1079.55</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>71.42%</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>23.95%</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>30.03%</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>17.59%</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>1020억</t>
+          <t>1129억</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2751,20 +2783,44 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>9000</v>
-      </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P28" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2773,79 +2829,53 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>1097.62</v>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>685.33</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5.29%</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>72.75%</t>
-        </is>
-      </c>
+        <v>6.92</v>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>58.44%</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>46.16%</t>
-        </is>
-      </c>
+          <t>39.43%</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>890억</t>
+          <t>1970억</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P29" t="n">
-        <v>24000</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>2.13%</t>
-        </is>
-      </c>
-      <c r="R29" t="n">
-        <v>14350</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>-40.21%</t>
-        </is>
-      </c>
+        <v>15000</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
@@ -2853,62 +2883,68 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>신한투자증권, 신한투자증권와</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1041.02</v>
+      </c>
       <c r="H30" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
+        <v>1252.9</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>95.20%</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>31.29%</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>1737억</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O30" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P30" t="n">
-        <v>4000</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-      <c r="R30" t="n">
-        <v>1905</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>-52.37%</t>
-        </is>
-      </c>
+        <v>15300</v>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
@@ -2916,127 +2952,89 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>494.62</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P31" t="n">
-        <v>21000</v>
+        <v>3415</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>70.75%</t>
         </is>
       </c>
       <c r="R31" t="n">
-        <v>15380</v>
+        <v>1937</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-43.28%</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>그외 기타 제품 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>한화투자증권</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3046,28 +3044,16 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>6.92</v>
+        <v>185.75</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>39.43%</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>1970억</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="n">
-        <v>15000</v>
+        <v>2000</v>
       </c>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -3080,7 +3066,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3089,267 +3075,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>일반 목적용 기계 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>신한투자증권, 신한투자증권와</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1041.02</v>
+        <v>101.91</v>
       </c>
       <c r="H33" t="n">
-        <v>1252.9</v>
+        <v>25.73</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>95.20%</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>31.29%</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1737억</t>
+          <t>1271억</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O33" t="n">
-        <v>15300</v>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+        <v>23000</v>
+      </c>
+      <c r="P33" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>스펙</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한국제17호스팩</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>금융 지원 서비스업</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P34" t="n">
-        <v>3415</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>70.75%</t>
-        </is>
-      </c>
-      <c r="R34" t="n">
-        <v>1937</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>28</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>스펙</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화플러스제6호스팩</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>기타 금융업</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화투자증권</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="n">
-        <v>185.75</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>14</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>해치텍</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>반도체 제조업</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>DB증권</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="H36" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
-      <c r="O36" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P36" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -2534,7 +2534,9 @@
       <c r="G25" t="n">
         <v>1234.3</v>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>1410.88</v>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -2181,10 +2181,22 @@
       <c r="O20" t="n">
         <v>7800</v>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>16000</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>105.13%</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>13620</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>-14.88%</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1178,7 +1178,9 @@
       <c r="G9" t="n">
         <v>284.53</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>3.55</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
@@ -2234,7 +2236,9 @@
       <c r="G21" t="n">
         <v>1000.07</v>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>684.73</v>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>0.87%</t>
@@ -2390,7 +2394,9 @@
       <c r="G23" t="n">
         <v>630.1</v>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>28.95</v>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>0.24%</t>
@@ -2866,13 +2872,21 @@
         <v>6.92</v>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.48%</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
           <t>39.43%</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>39.39%</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>1970억</t>
@@ -2928,20 +2942,28 @@
         <v>1041.02</v>
       </c>
       <c r="H30" t="n">
-        <v>1252.9</v>
+        <v>1253.39</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>95.20%</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>90.15%</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>31.29%</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>17.00%</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>1737억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1048,10 +1048,22 @@
       <c r="O7" t="n">
         <v>18500</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>32350</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>74.86%</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>26950</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>-16.69%</t>
+        </is>
+      </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -2942,7 +2954,7 @@
         <v>1041.02</v>
       </c>
       <c r="H30" t="n">
-        <v>1253.39</v>
+        <v>1252.9</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W33"/>
+  <dimension ref="A1:W34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1819,16 +1819,16 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>아이엠스팩1호</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1838,44 +1838,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SK증권</t>
+          <t>iM증권</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="n">
-        <v>656.02</v>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>14.83%</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>97.45%</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>86.61%</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>133억</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
         <v>2000</v>
       </c>
@@ -1890,7 +1868,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1899,53 +1877,47 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>KB증권, IBK투자증권</t>
+          <t>SK증권</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>714.52</v>
-      </c>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>666.78</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1.91%</t>
-        </is>
-      </c>
+        <v>656.02</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>34.58%</t>
+          <t>14.83%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>33.00%</t>
+          <t>97.45%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24.41%</t>
+          <t>86.61%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1673억</t>
+          <t>133억</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1954,24 +1926,12 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>21500</v>
-      </c>
-      <c r="P17" t="n">
-        <v>21500</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>14790</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>-31.21%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -1979,60 +1939,86 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>KB증권, IBK투자증권</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>714.52</v>
+      </c>
       <c r="H18" t="n">
-        <v>357</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>666.78</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.91%</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>34.58%</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>33.00%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>24.41%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1673억</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
       <c r="O18" t="n">
-        <v>2000</v>
+        <v>21500</v>
       </c>
       <c r="P18" t="n">
-        <v>4000</v>
+        <v>21500</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="R18" t="n">
-        <v>2075</v>
+        <v>14790</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>-48.12%</t>
+          <t>-31.21%</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2042,86 +2028,60 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>미래에셋증권, 삼성증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>388.84</v>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>408.16</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>13.70%</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>31.33%</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>20.77%</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>16.08%</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>10072억</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>90500</v>
+        <v>2000</v>
       </c>
       <c r="P19" t="n">
-        <v>75700</v>
+        <v>4000</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-16.35%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R19" t="n">
-        <v>61600</v>
+        <v>2075</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>-18.63%</t>
+          <t>-48.12%</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2131,7 +2091,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2140,51 +2100,53 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>미래에셋증권, 삼성증권</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>388.84</v>
+      </c>
       <c r="H20" t="n">
-        <v>1538.51</v>
+        <v>408.16</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30.62%</t>
+          <t>13.70%</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>82.52%</t>
+          <t>31.33%</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23.33%</t>
+          <t>20.77%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>14.72%</t>
+          <t>16.08%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2122억</t>
+          <t>10072억</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2193,22 +2155,22 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>7800</v>
+        <v>90500</v>
       </c>
       <c r="P20" t="n">
-        <v>16000</v>
+        <v>75700</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>105.13%</t>
+          <t>-16.35%</t>
         </is>
       </c>
       <c r="R20" t="n">
-        <v>13620</v>
+        <v>61600</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>-14.88%</t>
+          <t>-18.63%</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2218,7 +2180,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2227,45 +2189,51 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-11-02</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>1000.07</v>
-      </c>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>684.73</v>
+        <v>1538.51</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.87%</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>30.62%</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>82.52%</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>31.75%</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>23.33%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>14.72%</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1537억</t>
+          <t>2122억</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2274,12 +2242,24 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>17000</v>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
+        <v>7800</v>
+      </c>
+      <c r="P21" t="n">
+        <v>16000</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>105.13%</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>13620</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-14.88%</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
@@ -2287,7 +2267,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2296,53 +2276,45 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>기타 생활용품 소매업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-11-02</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1248.47</v>
+        <v>1000.07</v>
       </c>
       <c r="H22" t="n">
-        <v>1477.65</v>
+        <v>684.73</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.65%</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>55.61%</t>
-        </is>
-      </c>
+          <t>0.87%</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>21.08%</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>14.42%</t>
-        </is>
-      </c>
+          <t>31.75%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1202억</t>
+          <t>1537억</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2351,24 +2323,12 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P22" t="n">
-        <v>42750</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>256.25%</t>
-        </is>
-      </c>
-      <c r="R22" t="n">
-        <v>45700</v>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>6.90%</t>
-        </is>
-      </c>
+        <v>17000</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
@@ -2376,7 +2336,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2385,12 +2345,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>기타 생활용품 소매업</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2400,30 +2360,38 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>630.1</v>
+        <v>1248.47</v>
       </c>
       <c r="H23" t="n">
-        <v>28.95</v>
+        <v>1477.65</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>55.61%</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>37.62%</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>21.08%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>14.42%</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1728억</t>
+          <t>1202억</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2432,12 +2400,24 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>12400</v>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>42750</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>256.25%</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>45700</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>6.90%</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
@@ -2445,7 +2425,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2454,53 +2434,45 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-11-04</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>50.4</v>
+        <v>630.1</v>
       </c>
       <c r="H24" t="n">
-        <v>3.09</v>
+        <v>28.95</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2.23%</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>3.17%</t>
-        </is>
-      </c>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>25.60%</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>25.36%</t>
-        </is>
-      </c>
+          <t>37.62%</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5933억</t>
+          <t>1728억</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2509,24 +2481,12 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>12000</v>
-      </c>
-      <c r="P24" t="n">
-        <v>10960</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>-8.67%</t>
-        </is>
-      </c>
-      <c r="R24" t="n">
-        <v>17990</v>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>64.14%</t>
-        </is>
-      </c>
+        <v>12400</v>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
@@ -2534,7 +2494,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2543,41 +2503,53 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1234.3</v>
+        <v>50.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1410.88</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+        <v>3.09</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2.23%</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>3.17%</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>23.95%</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>25.60%</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>25.36%</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1020억</t>
+          <t>5933억</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2586,12 +2558,24 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>9000</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="P25" t="n">
+        <v>10960</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>-8.67%</t>
+        </is>
+      </c>
+      <c r="R25" t="n">
+        <v>17990</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>64.14%</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
@@ -2599,7 +2583,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2608,79 +2592,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1097.62</v>
+        <v>1234.3</v>
       </c>
       <c r="H26" t="n">
-        <v>685.33</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>5.29%</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>72.75%</t>
-        </is>
-      </c>
+        <v>1410.88</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>58.44%</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>46.16%</t>
-        </is>
-      </c>
+          <t>23.95%</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>890억</t>
+          <t>1020억</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>23500</v>
-      </c>
-      <c r="P26" t="n">
-        <v>24000</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>2.13%</t>
-        </is>
-      </c>
-      <c r="R26" t="n">
-        <v>14350</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>-40.21%</t>
-        </is>
-      </c>
+        <v>9000</v>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
@@ -2688,60 +2648,86 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1097.62</v>
+      </c>
       <c r="H27" t="n">
-        <v>397.33</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+        <v>685.33</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>72.75%</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>58.44%</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>46.16%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>890억</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O27" t="n">
-        <v>2000</v>
+        <v>23500</v>
       </c>
       <c r="P27" t="n">
-        <v>4000</v>
+        <v>24000</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="R27" t="n">
-        <v>1905</v>
+        <v>14350</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>-52.37%</t>
+          <t>-40.21%</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -2751,108 +2737,70 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IBK투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>938.24</v>
-      </c>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>1079.55</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>0.78%</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>71.42%</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>30.03%</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>17.59%</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>1129억</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>397.33</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="P28" t="n">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>90.91%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="R28" t="n">
-        <v>15380</v>
+        <v>1905</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>-26.76%</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>23450.0</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>113.18%</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>309228.0</t>
-        </is>
-      </c>
+          <t>-52.37%</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2861,47 +2809,53 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>그외 기타 제품 제조업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>IBK투자증권</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>938.24</v>
+      </c>
       <c r="H29" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>1079.55</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>71.42%</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>39.43%</t>
+          <t>30.03%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>39.39%</t>
+          <t>17.59%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1970억</t>
+          <t>1129억</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2910,20 +2864,44 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>15000</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
+        <v>11000</v>
+      </c>
+      <c r="P29" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>90.91%</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>15380</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-26.76%</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>23450.0</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>113.18%</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>309228.0</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -2932,62 +2910,56 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>일반 목적용 기계 제조업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>신한투자증권, 신한투자증권와</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1041.02</v>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>1252.9</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>95.20%</t>
-        </is>
-      </c>
+        <v>6.92</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>90.15%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>31.29%</t>
+          <t>39.43%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>17.00%</t>
+          <t>39.39%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1737억</t>
+          <t>1970억</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>유</t>
+          <t>무</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>15300</v>
+        <v>15000</v>
       </c>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -3000,62 +2972,76 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>스펙</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>신한투자증권, 신한투자증권와</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1041.02</v>
+      </c>
       <c r="H31" t="n">
-        <v>494.62</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+        <v>1252.9</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>95.20%</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>90.15%</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>31.29%</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>17.00%</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>1737억</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>유</t>
+        </is>
+      </c>
       <c r="O31" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P31" t="n">
-        <v>3415</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>70.75%</t>
-        </is>
-      </c>
-      <c r="R31" t="n">
-        <v>1937</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>-43.28%</t>
-        </is>
-      </c>
+        <v>15300</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
@@ -3063,7 +3049,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3072,27 +3058,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>한화투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>185.75</v>
+        <v>494.62</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -3103,10 +3089,22 @@
       <c r="O32" t="n">
         <v>2000</v>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>3415</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>70.75%</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>1937</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>-43.28%</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="inlineStr"/>
@@ -3114,93 +3112,144 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>스펙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한화투자증권</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>101.91</v>
-      </c>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>25.73</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>15.08%</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>5.63%</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>38.35%</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>37.69%</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>1271억</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>무</t>
-        </is>
-      </c>
+        <v>185.75</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>23000</v>
-      </c>
-      <c r="P33" t="n">
-        <v>20500</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>-10.87%</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
-        <v>13930</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>-32.05%</t>
-        </is>
-      </c>
+        <v>2000</v>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>14</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>해치텍</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>반도체 제조업</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>DB증권</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="H34" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>15.08%</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>5.63%</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>38.35%</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>37.69%</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1271억</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>무</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>23000</v>
+      </c>
+      <c r="P34" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>-10.87%</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>13930</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>-32.05%</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -2617,13 +2617,21 @@
         <v>1410.88</v>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>73.12%</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>23.95%</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>11.86%</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>1020억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1194,13 +1194,21 @@
         <v>3.55</v>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>12.74%</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>35.51%</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>34.13%</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>2768억</t>
@@ -1847,7 +1855,9 @@
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>1112.73</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -2305,13 +2315,21 @@
           <t>0.87%</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>37.17%</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>31.75%</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>24.78%</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>1537억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -1938,10 +1938,22 @@
       <c r="O17" t="n">
         <v>2000</v>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>4065</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>103.25%</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>1882</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>-53.70%</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
@@ -2481,13 +2493,21 @@
           <t>0.24%</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>14.02%</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>37.62%</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>35.96%</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>1728억</t>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -3084,10 +3084,22 @@
       <c r="O31" t="n">
         <v>15300</v>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>30350</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>98.37%</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>21000</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>-30.81%</t>
+        </is>
+      </c>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -3037,7 +3037,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>신한투자증권, 신한투자증권와</t>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">

--- a/ipo_watch_results.xlsx
+++ b/ipo_watch_results.xlsx
@@ -2683,10 +2683,22 @@
       <c r="O26" t="n">
         <v>9000</v>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>19290</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>114.33%</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>29150</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>51.11%</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
@@ -3007,10 +3019,22 @@
       <c r="O30" t="n">
         <v>15000</v>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>-20.00%</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>9000</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>-25.00%</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
@@ -3037,7 +3061,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>신한투자증권, 신한투자증권와</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3210,10 +3234,22 @@
       <c r="O33" t="n">
         <v>2000</v>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
+      <c r="P33" t="n">
+        <v>2810</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>40.50%</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>1866</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>-33.59%</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="inlineStr"/>
